--- a/data/processed/reconciliation_NEXLEV_2026-08.xlsx
+++ b/data/processed/reconciliation_NEXLEV_2026-08.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fee detail" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fee detail" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,1014 +427,626 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Section</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>% of sales</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>What it means</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1. SALES</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Units ordered (weekly report, order-date basis)</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>4892</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>different date basis from shipped</t>
-        </is>
-      </c>
+          <t>WHAT WE SOLD</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. SALES</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Units shipped (what Amazon paid on)</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>4133</v>
-      </c>
+          <t xml:space="preserve">  Units ordered</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4892</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>financial basis</t>
+          <t>on Amazon, 3P</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1. SALES</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ordered but not shipped</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>759</v>
-      </c>
+          <t xml:space="preserve">  Units Amazon shipped and paid on</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4133</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NOT all cancellations - month-end timing + pending orders; needs All-Orders report to split</t>
+          <t>the financial basis</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1. SALES</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Product sales (ex-GST)</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+          <t xml:space="preserve">  Product sales - GST NOT included</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>11621287.74</v>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>P&amp;L revenue</t>
+          <t>our revenue; every % below is against this</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1. SALES</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Shipping and gift wrap collected</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>66766.37</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t xml:space="preserve">  GST collected from customers</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2062051.32</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>17.7%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>held in trust - never ours</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2. RETURNS</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Units refunded</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>567</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t xml:space="preserve">  What customers actually paid</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>13683339.06</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>sales + GST = the money that came in</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2. RETURNS</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Return rate % (in-month, mixed cohorts)</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>13.72</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>these refunds mostly belong to earlier months' shipments</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2. RETURNS</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Sale value refunded (ex-GST)</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>-1753159.5</v>
-      </c>
+          <t>WHAT CAME BACK</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2. RETURNS</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Commission on refunds (ex-GST)</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>125100.29</v>
+          <t xml:space="preserve">  Units refunded</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>567</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>13.7%</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>given back to us</t>
+          <t>of units shipped</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2. RETURNS</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>FixedClosingFee on refunds (ex-GST)</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>12623</v>
+          <t xml:space="preserve">  Sale value refunded</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-1753159.5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>15.1%</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>given back to us</t>
+          <t>of sales</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2. RETURNS</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>GiftwrapChargeback on refunds (ex-GST)</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>25.42</v>
-      </c>
+          <t xml:space="preserve">  Fees Amazon gave back on those refunds</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>106869.05</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>given back to us</t>
+          <t>commission + closing returned; FBA fee never is</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2. RETURNS</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>RefundCommission on refunds (ex-GST)</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>-31750</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Amazon kept this</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2. RETURNS</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>ShippingChargeback on refunds (ex-GST)</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>870.34</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>given back to us</t>
-        </is>
-      </c>
+          <t>WHAT AMAZON DEDUCTED (before GST on fees)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Commission (referral)</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
+          <t xml:space="preserve">  Commission (referral)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>-826239.8100000001</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>7.1%</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>FBA fulfilment</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
+          <t xml:space="preserve">  FBA fulfilment (pick, pack, deliver)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
         <v>-596204.52</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
       </c>
       <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Closing fee</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
+          <t xml:space="preserve">  Closing fee</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
         <v>-177166</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Other selling fees</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>-4586.44</v>
+          <t xml:space="preserve">  Storage</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-111891.38</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1.0%</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>FBAStorageFee</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>-111891.38</v>
+          <t xml:space="preserve">  Long-term storage (aged stock)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-18510.93</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FBA Inventory Storage Fee</t>
+          <t>stock sitting too long</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>FBALongTermStorageFee</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>-18510.93</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>FBA Long Term Storage Fee</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  Removals and other service fees</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>-15105.44</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>FBARemovalFee</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>-9320</v>
+          <t xml:space="preserve">  TOTAL AMAZON FEES</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-1711657.45</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>14.7%</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FBA Removal Order: Return Fee</t>
+          <t>of sales, before GST on fees</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>MFNPostageFee</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>-1199</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>ServiceFee</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>TechnologyFee</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>RefusedDelivery</t>
-        </is>
-      </c>
+          <t>WHAT WE PAID FOR OURSELVES</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>TechnologyFee</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>ShippingAddressUndeliverable</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  Coupons and promotions</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-153674.29</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>TechnologyFee</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>UnableToDeliver</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  No-cost EMI / bank offers</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-69514.82000000001</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Subscription</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
+          <t xml:space="preserve">  Advertising</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>-1501598.67</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>12.9%</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ServiceFee</t>
+          <t>billed separately, not in settlement</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>FBAPerUnitFulfillmentFee</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>204.36</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>UnableToDeliver</t>
-        </is>
-      </c>
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>FBAWeightBasedFee</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1001</v>
+          <t>WHAT AMAZON PAID BACK</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>210889.26</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1.8%</t>
+        </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>UnableToDeliver</t>
+          <t>reimbursements for lost/damaged stock, fee corrections</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>FBAPerUnitFulfillmentFee</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1639.65</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>ShippingAddressUndeliverable</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>FBAPerUnitFulfillmentFee</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>4343.62</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>RefusedDelivery</t>
-        </is>
-      </c>
+          <t>TAX HELD BACK (not a cost - you get it back)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>FBAWeightBasedFee</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>7577</v>
-      </c>
+          <t xml:space="preserve">  TCS at 0.5% of net sales</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>-49015.15</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ShippingAddressUndeliverable</t>
+          <t>goes to your GST cash ledger - ACCEPT IT MONTHLY on the portal</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>FBAWeightBasedFee</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>18695</v>
-      </c>
+          <t xml:space="preserve">  TDS at 0.1% of gross sales</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-11592.94</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>RefusedDelivery</t>
+          <t>claim in your income tax return</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>4. WE FUNDED</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Coupons / promotions</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>-153674.29</v>
-      </c>
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4. WE FUNDED</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>No-cost EMI / bank offers</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>-69514.82000000001</v>
-      </c>
+          <t>THE BOTTOM LINE</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4. WE FUNDED</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Advertising (from our AMS data)</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>-1501598.67</v>
-      </c>
+          <t xml:space="preserve">  Amazon should pay us</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>9707251.27</v>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>billed outside settlement - CONFIRM if GST-inclusive</t>
+          <t>cash, including the GST we must pass on</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5. CREDITS</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Reversal Reimbursement</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>101864.35</v>
-      </c>
+          <t xml:space="preserve">  less GST we owe the government</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>-2011026.85</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>compensation - no GST</t>
+          <t>output GST less refunds, less credit on fee GST, less TCS</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5. CREDITS</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Free Replacement Refund Items</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>42851.01</v>
+          <t xml:space="preserve">  CONTRIBUTION BEFORE COST OF GOODS</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>7696224.42</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>66.2%</t>
+        </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>compensation - no GST</t>
+          <t>of sales</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5. CREDITS</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Lostordamagedreimbursement</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>1114.52</v>
+          <t xml:space="preserve">  After advertising</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>6194625.75</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>compensation - no GST</t>
+          <t>STILL NOT PROFIT - cost of goods not included</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>5. CREDITS</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Warehouse Damage</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>1821.61</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>compensation - no GST</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5. CREDITS</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Commissioncorrection</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>65468.13</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>fee credit - carries GST, reverses ITC</t>
-        </is>
-      </c>
+          <t>PROOF THIS IS COMPLETE</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5. CREDITS</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Payment Retraction Items</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>-2230.36</v>
-      </c>
+          <t xml:space="preserve">  Event types Amazon reported</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>6</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>compensation - no GST</t>
+          <t>every one classified above</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6. GST AND TAX (not profit)</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Output GST collected from customers</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>2062051.32</v>
-      </c>
+          <t xml:space="preserve">  Event types that were empty</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>27</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>held in trust - never ours</t>
+          <t>nothing ignored</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6. GST AND TAX (not profit)</t>
+          <t xml:space="preserve">  Settlement cycles tied to Amazon's own totals</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Output GST reversed on refunds</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>-310107.66</v>
-      </c>
-      <c r="D43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>6. GST AND TAX (not profit)</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>ITC on Amazon fees (reclaimable)</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>308098.34</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>tie to Amazon's tax invoice AND GSTR-2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>6. GST AND TAX (not profit)</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>TCS withheld u/s 52 (0.5% of net sales)</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>-49015.15</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>PREPAYMENT ASSET - accept monthly in the GST portal or it is stranded</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>6. GST AND TAX (not profit)</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>TDS withheld u/s 194-O (0.1% of gross)</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>-11592.94</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>RECOVERABLE in ITR - charged on gross, so returns are a permanent drag</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>6. GST AND TAX (not profit)</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Net GST still to remit in cash</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>-2011026.85</v>
-      </c>
-      <c r="D47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>7. BOTTOM LINE</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Amazon should settle (cash basis, GST-inclusive)</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>9707251.27</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>compare with deposits - cycles straddle the month end</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>7. BOTTOM LINE</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>less: net GST to remit to government</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>-2011026.85</v>
-      </c>
-      <c r="D49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>7. BOTTOM LINE</t>
-        </is>
-      </c>
-      <c r="B50">
-        <f> Marketplace contribution BEFORE COGS</f>
-        <v/>
-      </c>
-      <c r="C50" t="n">
-        <v>7696224.42</v>
-      </c>
-      <c r="D50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>7. BOTTOM LINE</t>
-        </is>
-      </c>
-      <c r="B51">
-        <f> After advertising, BEFORE COGS</f>
-        <v/>
-      </c>
-      <c r="C51" t="n">
-        <v>6194625.75</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>NOT profit - landed cost of goods is not in this file</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>9. COMPLETENESS</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Event lists Amazon returned with data</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>6</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>AdjustmentEventList, AffordabilityExpenseEventList, AffordabilityExpenseReversalEventList, RefundEventList, ServiceFeeEventList, ShipmentEventList</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>9. COMPLETENESS</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Event lists returned EMPTY</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>27</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>incl. ShipmentSettleEventList - must stay empty or revenue double-counts</t>
+          <t>12 of 12</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>each cycle matches to the paisa</t>
         </is>
       </c>
     </row>
@@ -1448,6 +1061,1030 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1. SALES</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Units ordered (weekly report, order-date basis)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>4892</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>different date basis from shipped</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1. SALES</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Units shipped (what Amazon paid on)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4133</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>financial basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1. SALES</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ordered but not shipped</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>759</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NOT all cancellations - month-end timing + pending orders; needs All-Orders report to split</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1. SALES</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Product sales (GST NOT included)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>11621287.74</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>P&amp;L revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1. SALES</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Shipping and gift wrap collected</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>66766.37</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2. RETURNS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Units refunded</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>567</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2. RETURNS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Return rate % (in-month, mixed cohorts)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>these refunds mostly belong to earlier months' shipments</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2. RETURNS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sale value refunded (GST NOT included)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>-1753159.5</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2. RETURNS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Commission on refunds (ex-GST)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>125100.29</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>given back to us</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2. RETURNS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FixedClosingFee on refunds (ex-GST)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>12623</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>given back to us</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2. RETURNS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GiftwrapChargeback on refunds (ex-GST)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>25.42</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>given back to us</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2. RETURNS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>RefundCommission on refunds (ex-GST)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>-31750</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Amazon kept this</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2. RETURNS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ShippingChargeback on refunds (ex-GST)</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>870.34</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>given back to us</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3. AMAZON FEES (ex-GST)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Commission (referral)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>-826239.8100000001</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3. AMAZON FEES (ex-GST)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FBA fulfilment</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>-596204.52</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3. AMAZON FEES (ex-GST)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Closing fee</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>-177166</v>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3. AMAZON FEES (ex-GST)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Other selling fees</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>-4586.44</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3. AMAZON FEES (ex-GST)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>FBAStorageFee</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>-111891.38</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>FBA Inventory Storage Fee</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3. AMAZON FEES (ex-GST)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FBALongTermStorageFee</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>-18510.93</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>FBA Long Term Storage Fee</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3. AMAZON FEES (ex-GST)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FBARemovalFee</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>-9320</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>FBA Removal Order: Return Fee</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3. AMAZON FEES (ex-GST)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MFNPostageFee</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>-1199</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ServiceFee</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>3. AMAZON FEES (ex-GST)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TechnologyFee</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>RefusedDelivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3. AMAZON FEES (ex-GST)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TechnologyFee</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ShippingAddressUndeliverable</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3. AMAZON FEES (ex-GST)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TechnologyFee</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>UnableToDeliver</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3. AMAZON FEES (ex-GST)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Subscription</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ServiceFee</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3. AMAZON FEES (ex-GST)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FBAPerUnitFulfillmentFee</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>204.36</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>UnableToDeliver</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3. AMAZON FEES (ex-GST)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FBAWeightBasedFee</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>UnableToDeliver</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3. AMAZON FEES (ex-GST)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FBAPerUnitFulfillmentFee</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1639.65</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ShippingAddressUndeliverable</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3. AMAZON FEES (ex-GST)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FBAPerUnitFulfillmentFee</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4343.62</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>RefusedDelivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>3. AMAZON FEES (ex-GST)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FBAWeightBasedFee</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>7577</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ShippingAddressUndeliverable</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>3. AMAZON FEES (ex-GST)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>FBAWeightBasedFee</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>18695</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>RefusedDelivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>4. WE FUNDED</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Coupons / promotions</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>-153674.29</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>4. WE FUNDED</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>No-cost EMI / bank offers</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>-69514.82000000001</v>
+      </c>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>4. WE FUNDED</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Advertising (from our AMS data)</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>-1501598.67</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>billed outside settlement - CONFIRM if GST-inclusive</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>5. CREDITS</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Reversal Reimbursement</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>101864.35</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>compensation - no GST</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>5. CREDITS</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Free Replacement Refund Items</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>42851.01</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>compensation - no GST</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>5. CREDITS</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Lostordamagedreimbursement</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1114.52</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>compensation - no GST</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>5. CREDITS</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Warehouse Damage</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1821.61</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>compensation - no GST</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>5. CREDITS</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Commissioncorrection</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>65468.13</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>fee credit - carries GST, reverses ITC</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>5. CREDITS</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Payment Retraction Items</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>-2230.36</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>compensation - no GST</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>6. GST AND TAX (not profit)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Output GST collected from customers</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2062051.32</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>held in trust - never ours</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>6. GST AND TAX (not profit)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Output GST reversed on refunds</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>-310107.66</v>
+      </c>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>6. GST AND TAX (not profit)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ITC on Amazon fees (reclaimable)</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>308098.34</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>tie to Amazon's tax invoice AND GSTR-2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>6. GST AND TAX (not profit)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>TCS withheld u/s 52 (0.5% of net sales)</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>-49015.15</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>PREPAYMENT ASSET - accept monthly in the GST portal or it is stranded</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>6. GST AND TAX (not profit)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>TDS withheld u/s 194-O (0.1% of gross)</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>-11592.94</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>RECOVERABLE in ITR - charged on gross, so returns are a permanent drag</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>6. GST AND TAX (not profit)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Net GST still to remit in cash</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>-2011026.85</v>
+      </c>
+      <c r="D47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>7. BOTTOM LINE</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Amazon should settle (cash basis, GST-inclusive)</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>9707251.27</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>compare with deposits - cycles straddle the month end</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>7. BOTTOM LINE</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>less: net GST to remit to government</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>-2011026.85</v>
+      </c>
+      <c r="D49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>7. BOTTOM LINE</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Marketplace contribution BEFORE COGS</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>7696224.42</v>
+      </c>
+      <c r="D50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>7. BOTTOM LINE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>After advertising, BEFORE COGS</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>6194625.75</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NOT profit - landed cost of goods is not in this file</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>9. COMPLETENESS</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Event lists Amazon returned with data</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>6</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdjustmentEventList, AffordabilityExpenseEventList, AffordabilityExpenseReversalEventList, RefundEventList, ServiceFeeEventList, ShipmentEventList</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>9. COMPLETENESS</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Event lists returned EMPTY</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>27</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>incl. ShipmentSettleEventList - must stay empty or revenue double-counts</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/data/processed/reconciliation_NEXLEV_2026-08.xlsx
+++ b/data/processed/reconciliation_NEXLEV_2026-08.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,219 +469,219 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4892</v>
+        <v>4459</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>on Amazon, 3P</t>
+          <t>orders placed this month</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Units Amazon shipped and paid on</t>
+          <t xml:space="preserve">  of which cancelled</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4133</v>
+        <v>-120</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>the financial basis</t>
+          <t>the real cancellation rate</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Product sales - GST NOT included</t>
+          <t xml:space="preserve">  of which not shipped by month end</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11621287.74</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
+        <v>-204</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>our revenue; every % below is against this</t>
+          <t>ships next month - timing, not lost</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  GST collected from customers</t>
+          <t xml:space="preserve">  Units Amazon shipped and paid on</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2062051.32</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>17.7%</t>
-        </is>
-      </c>
+        <v>4133</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>held in trust - never ours</t>
+          <t>the financial basis</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  What customers actually paid</t>
+          <t xml:space="preserve">  Product sales - GST NOT included</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13683339.06</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>11621287.74</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>sales + GST = the money that came in</t>
+          <t>our revenue; every % below is against this</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GST collected from customers</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2062051.32</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>17.7%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>held in trust - never ours</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WHAT CAME BACK</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t xml:space="preserve">  What customers actually paid</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>13683339.06</v>
+      </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>sales + GST = the money that came in</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Units refunded</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>567</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>13.7%</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>of units shipped</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Sale value refunded</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>-1753159.5</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>15.1%</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>of sales</t>
-        </is>
-      </c>
+          <t>WHAT CAME BACK</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Fees Amazon gave back on those refunds</t>
+          <t xml:space="preserve">  Units refunded</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>106869.05</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
+        <v>567</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>13.7%</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>commission + closing returned; FBA fee never is</t>
+          <t>of units shipped</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Sale value refunded</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-1753159.5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>15.1%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>of sales</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WHAT AMAZON DEDUCTED (before GST on fees)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+          <t xml:space="preserve">  Fees Amazon gave back on those refunds</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>106869.05</v>
+      </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>commission + closing returned; FBA fee never is</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Commission (referral)</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>-826239.8100000001</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>7.1%</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FBA fulfilment (pick, pack, deliver)</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>-596204.52</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>5.1%</t>
-        </is>
-      </c>
+          <t>WHAT AMAZON DEDUCTED (before GST on fees)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Closing fee</t>
+          <t xml:space="preserve">  Commission (referral)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-177166</v>
+        <v>-826239.8100000001</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -689,15 +689,15 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Storage</t>
+          <t xml:space="preserve">  FBA fulfilment (pick, pack, deliver)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-111891.38</v>
+        <v>-596204.52</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -705,146 +705,152 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Long-term storage (aged stock)</t>
+          <t xml:space="preserve">  Closing fee</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-18510.93</v>
+        <v>-177166</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>stock sitting too long</t>
-        </is>
-      </c>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Removals and other service fees</t>
+          <t xml:space="preserve">  Storage</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-15105.44</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
+        <v>-111891.38</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1.0%</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOTAL AMAZON FEES</t>
+          <t xml:space="preserve">  Long-term storage (aged stock)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-1711657.45</v>
+        <v>-18510.93</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>of sales, before GST on fees</t>
+          <t>stock sitting too long</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Removals and other service fees</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>-15105.44</v>
+      </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WHAT WE PAID FOR OURSELVES</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+          <t xml:space="preserve">  TOTAL AMAZON FEES</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-1711657.45</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>14.7%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>of sales, before GST on fees</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Coupons and promotions</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>-153674.29</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1.3%</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  No-cost EMI / bank offers</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>-69514.82000000001</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>WHAT WE PAID FOR OURSELVES</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Advertising</t>
+          <t xml:space="preserve">  Coupons and promotions</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1501598.67</v>
+        <v>-153674.29</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>12.9%</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>billed separately, not in settlement</t>
-        </is>
-      </c>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  No-cost EMI / bank offers</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-69514.82000000001</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>WHAT AMAZON PAID BACK</t>
+          <t xml:space="preserve">  Advertising</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>210889.26</v>
+        <v>-1501598.67</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>reimbursements for lost/damaged stock, fee corrections</t>
+          <t>billed separately, not in settlement</t>
         </is>
       </c>
     </row>
@@ -857,194 +863,220 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TAX HELD BACK (not a cost - you get it back)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+          <t>WHAT AMAZON PAID BACK</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>210889.26</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>reimbursements for lost/damaged stock, fee corrections</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TCS at 0.5% of net sales</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>-49015.15</v>
-      </c>
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>goes to your GST cash ledger - ACCEPT IT MONTHLY on the portal</t>
-        </is>
-      </c>
+      <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TDS at 0.1% of gross sales</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>-11592.94</v>
-      </c>
+          <t>TAX HELD BACK (not a cost - you get it back)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>claim in your income tax return</t>
-        </is>
-      </c>
+      <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TCS at 0.5% of net sales</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-49015.15</v>
+      </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>goes to your GST cash ledger - ACCEPT IT MONTHLY on the portal</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>THE BOTTOM LINE</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
+          <t xml:space="preserve">  TDS at 0.1% of gross sales</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-11592.94</v>
+      </c>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>claim in your income tax return</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Amazon should pay us</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>9707251.27</v>
-      </c>
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>cash, including the GST we must pass on</t>
-        </is>
-      </c>
+      <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  less GST we owe the government</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>-2011026.85</v>
-      </c>
+          <t>THE BOTTOM LINE</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>output GST less refunds, less credit on fee GST, less TCS</t>
-        </is>
-      </c>
+      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CONTRIBUTION BEFORE COST OF GOODS</t>
+          <t xml:space="preserve">  Amazon should pay us</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7696224.42</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>66.2%</t>
-        </is>
-      </c>
+        <v>9707251.27</v>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>of sales</t>
+          <t>cash, including the GST we must pass on</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">  After advertising</t>
+          <t xml:space="preserve">  less GST we owe the government</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>6194625.75</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>53.3%</t>
-        </is>
-      </c>
+        <v>-2011026.85</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>STILL NOT PROFIT - cost of goods not included</t>
+          <t>output GST less refunds, less credit on fee GST, less TCS</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CONTRIBUTION BEFORE COST OF GOODS</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>7696224.42</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>66.2%</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>of sales</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PROOF THIS IS COMPLETE</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+          <t xml:space="preserve">  After advertising</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>6194625.75</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>STILL NOT PROFIT - cost of goods not included</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Event types Amazon reported</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>6</v>
-      </c>
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>every one classified above</t>
-        </is>
-      </c>
+      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Event types that were empty</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>27</v>
-      </c>
+          <t>PROOF THIS IS COMPLETE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>nothing ignored</t>
-        </is>
-      </c>
+      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Settlement cycles tied to Amazon's own totals</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>12 of 12</t>
-        </is>
+          <t xml:space="preserve">  Event types Amazon reported</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>6</v>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
+        <is>
+          <t>every one classified above</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Event types that were empty</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>27</v>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>nothing ignored</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Settlement cycles tied to Amazon's own totals</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>12 of 12</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
         <is>
           <t>each cycle matches to the paisa</t>
         </is>
@@ -1061,7 +1093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1094,15 +1126,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Units ordered (weekly report, order-date basis)</t>
+          <t>Units ordered in the month</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4892</v>
+        <v>4459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>different date basis from shipped</t>
+          <t>All-Orders report, order date</t>
         </is>
       </c>
     </row>
@@ -1114,15 +1146,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Units shipped (what Amazon paid on)</t>
+          <t xml:space="preserve">  less cancelled</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4133</v>
+        <v>-120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>financial basis</t>
+          <t>2.7% of orders - the REAL cancellation rate</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1166,13 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ordered but not shipped</t>
+          <t xml:space="preserve">  less pending (payment not authorised)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>759</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NOT all cancellations - month-end timing + pending orders; needs All-Orders report to split</t>
-        </is>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1154,17 +1182,13 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Product sales (GST NOT included)</t>
+          <t xml:space="preserve">  less unfulfillable</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11621287.74</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>P&amp;L revenue</t>
-        </is>
-      </c>
+        <v>-3</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1174,85 +1198,88 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shipping and gift wrap collected</t>
+          <t xml:space="preserve">  less not shipped by month end</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>66766.37</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+        <v>-204</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ships next month</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2. RETURNS</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Units refunded</t>
-        </is>
+          <t>1. SALES</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f> Shipped from this month's orders</f>
+        <v/>
       </c>
       <c r="C7" t="n">
-        <v>567</v>
+        <v>4131</v>
       </c>
       <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2. RETURNS</t>
+          <t>1. SALES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Return rate % (in-month, mixed cohorts)</t>
+          <t>Units shipped (what Amazon paid on)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13.72</v>
+        <v>4133</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>these refunds mostly belong to earlier months' shipments</t>
+          <t>financial basis; differs from 4131 by cross-month timing</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2. RETURNS</t>
+          <t>1. SALES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sale value refunded (GST NOT included)</t>
+          <t>Product sales (GST NOT included)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-1753159.5</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>11621287.74</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>P&amp;L revenue</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2. RETURNS</t>
+          <t>1. SALES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Commission on refunds (ex-GST)</t>
+          <t>Shipping and gift wrap collected</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>125100.29</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>given back to us</t>
-        </is>
-      </c>
+        <v>66766.37</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1262,17 +1289,13 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FixedClosingFee on refunds (ex-GST)</t>
+          <t>Units refunded</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12623</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>given back to us</t>
-        </is>
-      </c>
+        <v>567</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1282,15 +1305,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GiftwrapChargeback on refunds (ex-GST)</t>
+          <t>Return rate % (in-month, mixed cohorts)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25.42</v>
+        <v>13.72</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>given back to us</t>
+          <t>these refunds mostly belong to earlier months' shipments</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1325,13 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RefundCommission on refunds (ex-GST)</t>
+          <t>Sale value refunded (GST NOT included)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-31750</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Amazon kept this</t>
-        </is>
-      </c>
+        <v>-1753159.5</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1322,11 +1341,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ShippingChargeback on refunds (ex-GST)</t>
+          <t>Commission on refunds (ex-GST)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>870.34</v>
+        <v>125100.29</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1337,66 +1356,82 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
+          <t>2. RETURNS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Commission (referral)</t>
+          <t>FixedClosingFee on refunds (ex-GST)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-826239.8100000001</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
+        <v>12623</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>given back to us</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
+          <t>2. RETURNS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FBA fulfilment</t>
+          <t>GiftwrapChargeback on refunds (ex-GST)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-596204.52</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
+        <v>25.42</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>given back to us</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
+          <t>2. RETURNS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Closing fee</t>
+          <t>RefundCommission on refunds (ex-GST)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-177166</v>
-      </c>
-      <c r="D17" t="inlineStr"/>
+        <v>-31750</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Amazon kept this</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
+          <t>2. RETURNS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Other selling fees</t>
+          <t>ShippingChargeback on refunds (ex-GST)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-4586.44</v>
-      </c>
-      <c r="D18" t="inlineStr"/>
+        <v>870.34</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>given back to us</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1406,17 +1441,13 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FBAStorageFee</t>
+          <t>Commission (referral)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-111891.38</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>FBA Inventory Storage Fee</t>
-        </is>
-      </c>
+        <v>-826239.8100000001</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1426,17 +1457,13 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FBALongTermStorageFee</t>
+          <t>FBA fulfilment</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-18510.93</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>FBA Long Term Storage Fee</t>
-        </is>
-      </c>
+        <v>-596204.52</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1446,17 +1473,13 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FBARemovalFee</t>
+          <t>Closing fee</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-9320</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>FBA Removal Order: Return Fee</t>
-        </is>
-      </c>
+        <v>-177166</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1466,17 +1489,13 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MFNPostageFee</t>
+          <t>Other selling fees</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-1199</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>ServiceFee</t>
-        </is>
-      </c>
+        <v>-4586.44</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1486,15 +1505,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TechnologyFee</t>
+          <t>FBAStorageFee</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>-111891.38</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>RefusedDelivery</t>
+          <t>FBA Inventory Storage Fee</t>
         </is>
       </c>
     </row>
@@ -1506,15 +1525,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TechnologyFee</t>
+          <t>FBALongTermStorageFee</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>-18510.93</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ShippingAddressUndeliverable</t>
+          <t>FBA Long Term Storage Fee</t>
         </is>
       </c>
     </row>
@@ -1526,15 +1545,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TechnologyFee</t>
+          <t>FBARemovalFee</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>-9320</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>UnableToDeliver</t>
+          <t>FBA Removal Order: Return Fee</t>
         </is>
       </c>
     </row>
@@ -1546,11 +1565,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Subscription</t>
+          <t>MFNPostageFee</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>-1199</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1566,15 +1585,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FBAPerUnitFulfillmentFee</t>
+          <t>TechnologyFee</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>204.36</v>
+        <v>0</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>UnableToDeliver</t>
+          <t>RefusedDelivery</t>
         </is>
       </c>
     </row>
@@ -1586,15 +1605,15 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FBAWeightBasedFee</t>
+          <t>TechnologyFee</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>UnableToDeliver</t>
+          <t>ShippingAddressUndeliverable</t>
         </is>
       </c>
     </row>
@@ -1606,15 +1625,15 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FBAPerUnitFulfillmentFee</t>
+          <t>TechnologyFee</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1639.65</v>
+        <v>0</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ShippingAddressUndeliverable</t>
+          <t>UnableToDeliver</t>
         </is>
       </c>
     </row>
@@ -1626,15 +1645,15 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FBAPerUnitFulfillmentFee</t>
+          <t>Subscription</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4343.62</v>
+        <v>0</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>RefusedDelivery</t>
+          <t>ServiceFee</t>
         </is>
       </c>
     </row>
@@ -1646,15 +1665,15 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FBAWeightBasedFee</t>
+          <t>FBAPerUnitFulfillmentFee</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7577</v>
+        <v>204.36</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ShippingAddressUndeliverable</t>
+          <t>UnableToDeliver</t>
         </is>
       </c>
     </row>
@@ -1670,143 +1689,143 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>18695</v>
+        <v>1001</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>RefusedDelivery</t>
+          <t>UnableToDeliver</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4. WE FUNDED</t>
+          <t>3. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Coupons / promotions</t>
+          <t>FBAPerUnitFulfillmentFee</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-153674.29</v>
-      </c>
-      <c r="D33" t="inlineStr"/>
+        <v>1639.65</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ShippingAddressUndeliverable</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4. WE FUNDED</t>
+          <t>3. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>No-cost EMI / bank offers</t>
+          <t>FBAPerUnitFulfillmentFee</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-69514.82000000001</v>
-      </c>
-      <c r="D34" t="inlineStr"/>
+        <v>4343.62</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>RefusedDelivery</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4. WE FUNDED</t>
+          <t>3. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Advertising (from our AMS data)</t>
+          <t>FBAWeightBasedFee</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-1501598.67</v>
+        <v>7577</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>billed outside settlement - CONFIRM if GST-inclusive</t>
+          <t>ShippingAddressUndeliverable</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5. CREDITS</t>
+          <t>3. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Reversal Reimbursement</t>
+          <t>FBAWeightBasedFee</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>101864.35</v>
+        <v>18695</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>compensation - no GST</t>
+          <t>RefusedDelivery</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5. CREDITS</t>
+          <t>4. WE FUNDED</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Free Replacement Refund Items</t>
+          <t>Coupons / promotions</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>42851.01</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>compensation - no GST</t>
-        </is>
-      </c>
+        <v>-153674.29</v>
+      </c>
+      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5. CREDITS</t>
+          <t>4. WE FUNDED</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lostordamagedreimbursement</t>
+          <t>No-cost EMI / bank offers</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1114.52</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>compensation - no GST</t>
-        </is>
-      </c>
+        <v>-69514.82000000001</v>
+      </c>
+      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5. CREDITS</t>
+          <t>4. WE FUNDED</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Warehouse Damage</t>
+          <t>Advertising (from our AMS data)</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1821.61</v>
+        <v>-1501598.67</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>compensation - no GST</t>
+          <t>billed outside settlement - CONFIRM if GST-inclusive</t>
         </is>
       </c>
     </row>
@@ -1818,15 +1837,15 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Commissioncorrection</t>
+          <t>Reversal Reimbursement</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>65468.13</v>
+        <v>101864.35</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>fee credit - carries GST, reverses ITC</t>
+          <t>compensation - no GST</t>
         </is>
       </c>
     </row>
@@ -1838,11 +1857,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Payment Retraction Items</t>
+          <t>Free Replacement Refund Items</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-2230.36</v>
+        <v>42851.01</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1853,76 +1872,80 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6. GST AND TAX (not profit)</t>
+          <t>5. CREDITS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Output GST collected from customers</t>
+          <t>Lostordamagedreimbursement</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2062051.32</v>
+        <v>1114.52</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>held in trust - never ours</t>
+          <t>compensation - no GST</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6. GST AND TAX (not profit)</t>
+          <t>5. CREDITS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Output GST reversed on refunds</t>
+          <t>Warehouse Damage</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-310107.66</v>
-      </c>
-      <c r="D43" t="inlineStr"/>
+        <v>1821.61</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>compensation - no GST</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6. GST AND TAX (not profit)</t>
+          <t>5. CREDITS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ITC on Amazon fees (reclaimable)</t>
+          <t>Commissioncorrection</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>308098.34</v>
+        <v>65468.13</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tie to Amazon's tax invoice AND GSTR-2B</t>
+          <t>fee credit - carries GST, reverses ITC</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6. GST AND TAX (not profit)</t>
+          <t>5. CREDITS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TCS withheld u/s 52 (0.5% of net sales)</t>
+          <t>Payment Retraction Items</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-49015.15</v>
+        <v>-2230.36</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>PREPAYMENT ASSET - accept monthly in the GST portal or it is stranded</t>
+          <t>compensation - no GST</t>
         </is>
       </c>
     </row>
@@ -1934,15 +1957,15 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TDS withheld u/s 194-O (0.1% of gross)</t>
+          <t>Output GST collected from customers</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-11592.94</v>
+        <v>2062051.32</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>RECOVERABLE in ITR - charged on gross, so returns are a permanent drag</t>
+          <t>held in trust - never ours</t>
         </is>
       </c>
     </row>
@@ -1954,121 +1977,429 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Net GST still to remit in cash</t>
+          <t>Output GST reversed on refunds</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-2011026.85</v>
+        <v>-310107.66</v>
       </c>
       <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7. BOTTOM LINE</t>
+          <t>6. GST AND TAX (not profit)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Amazon should settle (cash basis, GST-inclusive)</t>
+          <t>ITC on Amazon fees (reclaimable)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>9707251.27</v>
+        <v>308098.34</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>compare with deposits - cycles straddle the month end</t>
+          <t>tie to Amazon's tax invoice AND GSTR-2B</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7. BOTTOM LINE</t>
+          <t>6. GST AND TAX (not profit)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>less: net GST to remit to government</t>
+          <t>TCS withheld u/s 52 (0.5% of net sales)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-2011026.85</v>
-      </c>
-      <c r="D49" t="inlineStr"/>
+        <v>-49015.15</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>PREPAYMENT ASSET - accept monthly in the GST portal or it is stranded</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7. BOTTOM LINE</t>
+          <t>6. GST AND TAX (not profit)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Marketplace contribution BEFORE COGS</t>
+          <t>TDS withheld u/s 194-O (0.1% of gross)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7696224.42</v>
-      </c>
-      <c r="D50" t="inlineStr"/>
+        <v>-11592.94</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>RECOVERABLE in ITR - charged on gross, so returns are a permanent drag</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7. BOTTOM LINE</t>
+          <t>6. GST AND TAX (not profit)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>After advertising, BEFORE COGS</t>
+          <t>Net GST still to remit in cash</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6194625.75</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>NOT profit - landed cost of goods is not in this file</t>
-        </is>
-      </c>
+        <v>-2011026.85</v>
+      </c>
+      <c r="D51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>9. COMPLETENESS</t>
+          <t>7. HOW THE TOTAL IS BUILT</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Event lists Amazon returned with data</t>
+          <t>Product sales (GST not included)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
+        <v>11621287.74</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>AdjustmentEventList, AffordabilityExpenseEventList, AffordabilityExpenseReversalEventList, RefundEventList, ServiceFeeEventList, ShipmentEventList</t>
+          <t>what we sold</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>9. COMPLETENESS</t>
+          <t>7. HOW THE TOTAL IS BUILT</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>plus GST collected from customers</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2062051.32</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>comes in with the sale, goes out to the government</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>7. HOW THE TOTAL IS BUILT</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>plus shipping and gift wrap</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>66766.37</v>
+      </c>
+      <c r="D54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>7. HOW THE TOTAL IS BUILT</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>less refunds to customers</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>-2076295.91</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>sale value + GST returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>7. HOW THE TOTAL IS BUILT</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>plus fees Amazon returned on refunds</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>126105.48</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>commission and closing come back; FBA fee does not</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>7. HOW THE TOTAL IS BUILT</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>less Amazon fees (including GST on fees)</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>-2019755.79</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>commission, FBA, closing, storage, removals</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>7. HOW THE TOTAL IS BUILT</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>less coupons and promotions</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>-153674.29</v>
+      </c>
+      <c r="D58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>7. HOW THE TOTAL IS BUILT</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>less no-cost EMI and bank offers</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>-69514.82000000001</v>
+      </c>
+      <c r="D59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>7. HOW THE TOTAL IS BUILT</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>plus reimbursements and corrections</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>210889.26</v>
+      </c>
+      <c r="D60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>7. HOW THE TOTAL IS BUILT</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>less TCS withheld</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>-49015.15</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>you reclaim this in GST</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>7. HOW THE TOTAL IS BUILT</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>less TDS withheld</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>-11592.94</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>you reclaim this in your ITR</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>8. BOTTOM LINE</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>AMAZON SHOULD PAY US</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>9707251.27</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>add up everything above - this is the settlement</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>8. BOTTOM LINE</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>less GST we owe the government</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>-2011026.85</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>output GST, less GST refunded, less credit on fee GST, less TCS already withheld</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>8. BOTTOM LINE</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>MARKETPLACE CONTRIBUTION BEFORE COGS</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>7696224.42</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>what the marketplace actually left us</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>8. BOTTOM LINE</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>less advertising</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>-1501598.67</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>billed separately by Amazon Ads, never in the settlement</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>8. BOTTOM LINE</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>AFTER ADVERTISING, BEFORE COGS</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>6194625.75</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NOT profit - the landed cost of the goods still has to come off</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>10. COMPLETENESS</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Event lists Amazon returned with data</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>6</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdjustmentEventList, AffordabilityExpenseEventList, AffordabilityExpenseReversalEventList, RefundEventList, ServiceFeeEventList, ShipmentEventList</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>10. COMPLETENESS</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>Event lists returned EMPTY</t>
         </is>
       </c>
-      <c r="C53" t="n">
+      <c r="C69" t="n">
         <v>27</v>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>incl. ShipmentSettleEventList - must stay empty or revenue double-counts</t>
         </is>

--- a/data/processed/reconciliation_NEXLEV_2026-08.xlsx
+++ b/data/processed/reconciliation_NEXLEV_2026-08.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -841,11 +841,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1501598.67</v>
+        <v>0</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2011026.85</v>
+        <v>-1165772.75</v>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
@@ -983,11 +983,11 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7696224.42</v>
+        <v>8541478.52</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1003,80 +1003,172 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>6194625.75</v>
+        <v>8541478.52</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>STILL NOT PROFIT - cost of goods not included</t>
+          <t>before cost of goods</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  less cost of goods (net of returns recovered)</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>-5747318.6</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>49.5%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>landed cost from the margin master</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PROOF THIS IS COMPLETE</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
+          <t xml:space="preserve">  AMAZON CHANNEL CONTRIBUTION</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1304154.2</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>11.2%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>before company overhead, interest and tax</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Event types Amazon reported</t>
+          <t xml:space="preserve">  less business overhead and finance</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>6</v>
+        <v>-929703.02</v>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>every one classified above</t>
+          <t>rates from the margin master</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Event types that were empty</t>
+          <t xml:space="preserve">  PROFIT BEFORE TAX</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>27</v>
-      </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>nothing ignored</t>
-        </is>
-      </c>
+        <v>374451.18</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t xml:space="preserve">  PROFIT AFTER TAX</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>280209.31</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2.4%</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Amazon 3P only, this month</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PROOF THIS IS COMPLETE</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Event types Amazon reported</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>6</v>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>every one classified above</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Event types that were empty</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>27</v>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>nothing ignored</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Settlement cycles tied to Amazon's own totals</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>12 of 12</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr">
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
         <is>
           <t>each cycle matches to the paisa</t>
         </is>
@@ -1093,7 +1185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1121,7 +1213,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1. SALES</t>
+          <t>01. SALES</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1141,7 +1233,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. SALES</t>
+          <t>01. SALES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1161,7 +1253,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1. SALES</t>
+          <t>01. SALES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +1269,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1. SALES</t>
+          <t>01. SALES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1193,7 +1285,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1. SALES</t>
+          <t>01. SALES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1213,7 +1305,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1. SALES</t>
+          <t>01. SALES</t>
         </is>
       </c>
       <c r="B7">
@@ -1228,7 +1320,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1. SALES</t>
+          <t>01. SALES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1248,7 +1340,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1. SALES</t>
+          <t>01. SALES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1268,7 +1360,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1. SALES</t>
+          <t>01. SALES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1284,7 +1376,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2. RETURNS</t>
+          <t>02. RETURNS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1300,7 +1392,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2. RETURNS</t>
+          <t>02. RETURNS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1320,7 +1412,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2. RETURNS</t>
+          <t>02. RETURNS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1336,7 +1428,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2. RETURNS</t>
+          <t>02. RETURNS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1356,7 +1448,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2. RETURNS</t>
+          <t>02. RETURNS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1376,7 +1468,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2. RETURNS</t>
+          <t>02. RETURNS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1396,7 +1488,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2. RETURNS</t>
+          <t>02. RETURNS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1416,7 +1508,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2. RETURNS</t>
+          <t>02. RETURNS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1436,7 +1528,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
+          <t>03. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1452,7 +1544,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
+          <t>03. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1468,7 +1560,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
+          <t>03. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1484,7 +1576,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
+          <t>03. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1500,7 +1592,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
+          <t>03. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1520,7 +1612,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
+          <t>03. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1540,7 +1632,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
+          <t>03. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1560,7 +1652,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
+          <t>03. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1580,7 +1672,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
+          <t>03. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1600,7 +1692,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
+          <t>03. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1620,7 +1712,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
+          <t>03. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1640,7 +1732,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
+          <t>03. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1660,7 +1752,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
+          <t>03. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1680,7 +1772,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
+          <t>03. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1700,7 +1792,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
+          <t>03. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1720,7 +1812,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
+          <t>03. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1740,7 +1832,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
+          <t>03. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1760,7 +1852,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3. AMAZON FEES (ex-GST)</t>
+          <t>03. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1780,7 +1872,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4. WE FUNDED</t>
+          <t>04. WE FUNDED</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1796,7 +1888,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4. WE FUNDED</t>
+          <t>04. WE FUNDED</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1812,12 +1904,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4. WE FUNDED</t>
+          <t>04. WE FUNDED</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Advertising (from our AMS data)</t>
+          <t>Advertising (billed with GST)</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1825,63 +1917,63 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>billed outside settlement - CONFIRM if GST-inclusive</t>
+          <t>what Amazon Ads actually charged us, GST included</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5. CREDITS</t>
+          <t>04. WE FUNDED</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Reversal Reimbursement</t>
+          <t xml:space="preserve">  of which GST we get back as credit</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>101864.35</v>
+        <v>229057.42</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>compensation - no GST</t>
+          <t>reclaimed below - the real cost of ads is the ex-GST figure</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5. CREDITS</t>
+          <t>04. WE FUNDED</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Free Replacement Refund Items</t>
+          <t xml:space="preserve">  real cost of advertising (ex-GST)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>42851.01</v>
+        <v>-1272541.24</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>compensation - no GST</t>
+          <t>11.0% of sales</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5. CREDITS</t>
+          <t>05. CREDITS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lostordamagedreimbursement</t>
+          <t>Reversal Reimbursement</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1114.52</v>
+        <v>101864.35</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1892,16 +1984,16 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5. CREDITS</t>
+          <t>05. CREDITS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Warehouse Damage</t>
+          <t>Free Replacement Refund Items</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1821.61</v>
+        <v>42851.01</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1912,36 +2004,36 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5. CREDITS</t>
+          <t>05. CREDITS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Commissioncorrection</t>
+          <t>Lostordamagedreimbursement</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>65468.13</v>
+        <v>1114.52</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>fee credit - carries GST, reverses ITC</t>
+          <t>compensation - no GST</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5. CREDITS</t>
+          <t>05. CREDITS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Payment Retraction Items</t>
+          <t>Warehouse Damage</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-2230.36</v>
+        <v>1821.61</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1952,454 +2044,710 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6. GST AND TAX (not profit)</t>
+          <t>05. CREDITS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Output GST collected from customers</t>
+          <t>Commissioncorrection</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2062051.32</v>
+        <v>65468.13</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>held in trust - never ours</t>
+          <t>fee credit - carries GST, reverses ITC</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6. GST AND TAX (not profit)</t>
+          <t>05. CREDITS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Output GST reversed on refunds</t>
+          <t>Payment Retraction Items</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-310107.66</v>
-      </c>
-      <c r="D47" t="inlineStr"/>
+        <v>-2230.36</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>compensation - no GST</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6. GST AND TAX (not profit)</t>
+          <t>06. GST AND TAX (not profit)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ITC on Amazon fees (reclaimable)</t>
+          <t>Output GST collected from customers</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>308098.34</v>
+        <v>2062051.32</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tie to Amazon's tax invoice AND GSTR-2B</t>
+          <t>held in trust - never ours</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6. GST AND TAX (not profit)</t>
+          <t>06. GST AND TAX (not profit)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TCS withheld u/s 52 (0.5% of net sales)</t>
+          <t>Output GST reversed on refunds</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-49015.15</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>PREPAYMENT ASSET - accept monthly in the GST portal or it is stranded</t>
-        </is>
-      </c>
+        <v>-310107.66</v>
+      </c>
+      <c r="D49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6. GST AND TAX (not profit)</t>
+          <t>06. GST AND TAX (not profit)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TDS withheld u/s 194-O (0.1% of gross)</t>
+          <t>ITC on Amazon fees (reclaimable)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-11592.94</v>
+        <v>308098.34</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>RECOVERABLE in ITR - charged on gross, so returns are a permanent drag</t>
+          <t>tie to Amazon's tax invoice AND GSTR-2B</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6. GST AND TAX (not profit)</t>
+          <t>06. GST AND TAX (not profit)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Net GST still to remit in cash</t>
+          <t>ITC on advertising (reclaimable)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-2011026.85</v>
-      </c>
-      <c r="D51" t="inlineStr"/>
+        <v>229057.42</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ad invoices carry GST too - claim it in GSTR-2B or you pay 18% twice</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>7. HOW THE TOTAL IS BUILT</t>
+          <t>06. GST AND TAX (not profit)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Product sales (GST not included)</t>
+          <t>TCS withheld u/s 52 (0.5% of net sales)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>11621287.74</v>
+        <v>-49015.15</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>what we sold</t>
+          <t>PREPAYMENT ASSET - accept monthly in the GST portal or it is stranded</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7. HOW THE TOTAL IS BUILT</t>
+          <t>06. GST AND TAX (not profit)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>plus GST collected from customers</t>
+          <t>TDS withheld u/s 194-O (0.1% of gross)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2062051.32</v>
+        <v>-11592.94</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>comes in with the sale, goes out to the government</t>
+          <t>RECOVERABLE in ITR - charged on gross, so returns are a permanent drag</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7. HOW THE TOTAL IS BUILT</t>
+          <t>06. GST AND TAX (not profit)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>plus shipping and gift wrap</t>
+          <t>Net GST still to remit in cash</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>66766.37</v>
+        <v>-1165772.75</v>
       </c>
       <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7. HOW THE TOTAL IS BUILT</t>
+          <t>07. HOW THE TOTAL IS BUILT</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>less refunds to customers</t>
+          <t>Product sales (GST not included)</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-2076295.91</v>
+        <v>11621287.74</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>sale value + GST returned</t>
+          <t>what we sold</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7. HOW THE TOTAL IS BUILT</t>
+          <t>07. HOW THE TOTAL IS BUILT</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>plus fees Amazon returned on refunds</t>
+          <t>plus GST collected from customers</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>126105.48</v>
+        <v>2062051.32</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>commission and closing come back; FBA fee does not</t>
+          <t>comes in with the sale, goes out to the government</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>7. HOW THE TOTAL IS BUILT</t>
+          <t>07. HOW THE TOTAL IS BUILT</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>less Amazon fees (including GST on fees)</t>
+          <t>plus shipping and gift wrap</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-2019755.79</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>commission, FBA, closing, storage, removals</t>
-        </is>
-      </c>
+        <v>66766.37</v>
+      </c>
+      <c r="D57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7. HOW THE TOTAL IS BUILT</t>
+          <t>07. HOW THE TOTAL IS BUILT</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>less coupons and promotions</t>
+          <t>less refunds to customers</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-153674.29</v>
-      </c>
-      <c r="D58" t="inlineStr"/>
+        <v>-2076295.91</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>sale value + GST returned</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>7. HOW THE TOTAL IS BUILT</t>
+          <t>07. HOW THE TOTAL IS BUILT</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>less no-cost EMI and bank offers</t>
+          <t>plus fees Amazon returned on refunds</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-69514.82000000001</v>
-      </c>
-      <c r="D59" t="inlineStr"/>
+        <v>126105.48</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>commission and closing come back; FBA fee does not</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>7. HOW THE TOTAL IS BUILT</t>
+          <t>07. HOW THE TOTAL IS BUILT</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>plus reimbursements and corrections</t>
+          <t>less Amazon fees (including GST on fees)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>210889.26</v>
-      </c>
-      <c r="D60" t="inlineStr"/>
+        <v>-2019755.79</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>commission, FBA, closing, storage, removals</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>7. HOW THE TOTAL IS BUILT</t>
+          <t>07. HOW THE TOTAL IS BUILT</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>less TCS withheld</t>
+          <t>less coupons and promotions</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-49015.15</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>you reclaim this in GST</t>
-        </is>
-      </c>
+        <v>-153674.29</v>
+      </c>
+      <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>7. HOW THE TOTAL IS BUILT</t>
+          <t>07. HOW THE TOTAL IS BUILT</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>less TDS withheld</t>
+          <t>less no-cost EMI and bank offers</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-11592.94</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>you reclaim this in your ITR</t>
-        </is>
-      </c>
+        <v>-69514.82000000001</v>
+      </c>
+      <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>8. BOTTOM LINE</t>
+          <t>07. HOW THE TOTAL IS BUILT</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AMAZON SHOULD PAY US</t>
+          <t>plus reimbursements and corrections</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>9707251.27</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>add up everything above - this is the settlement</t>
-        </is>
-      </c>
+        <v>210889.26</v>
+      </c>
+      <c r="D63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>8. BOTTOM LINE</t>
+          <t>07. HOW THE TOTAL IS BUILT</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>less GST we owe the government</t>
+          <t>less TCS withheld</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-2011026.85</v>
+        <v>-49015.15</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>output GST, less GST refunded, less credit on fee GST, less TCS already withheld</t>
+          <t>you reclaim this in GST</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>8. BOTTOM LINE</t>
+          <t>07. HOW THE TOTAL IS BUILT</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MARKETPLACE CONTRIBUTION BEFORE COGS</t>
+          <t>less TDS withheld</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>7696224.42</v>
+        <v>-11592.94</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>what the marketplace actually left us</t>
+          <t>you reclaim this in your ITR</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>8. BOTTOM LINE</t>
+          <t>08. BOTTOM LINE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>less advertising</t>
+          <t>AMAZON SHOULD PAY US</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-1501598.67</v>
+        <v>9707251.27</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>billed separately by Amazon Ads, never in the settlement</t>
+          <t>add up everything above - this is the settlement</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>8. BOTTOM LINE</t>
+          <t>08. BOTTOM LINE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AFTER ADVERTISING, BEFORE COGS</t>
+          <t>less GST we owe the government</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>6194625.75</v>
+        <v>-1165772.75</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NOT profit - the landed cost of the goods still has to come off</t>
+          <t>output GST, less refunds, less credit on fee GST and ad GST, less TCS withheld</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10. COMPLETENESS</t>
+          <t>08. BOTTOM LINE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Event lists Amazon returned with data</t>
+          <t>MARKETPLACE CONTRIBUTION BEFORE COGS</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>6</v>
+        <v>8541478.52</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>AdjustmentEventList, AffordabilityExpenseEventList, AffordabilityExpenseReversalEventList, RefundEventList, ServiceFeeEventList, ShipmentEventList</t>
+          <t>what the marketplace actually left us</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10. COMPLETENESS</t>
+          <t>08. BOTTOM LINE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
+          <t>less advertising (GST-inclusive cash)</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>-1501598.67</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>billed separately by Amazon Ads; its GST is credited back in the line above</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>08. BOTTOM LINE</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>AFTER ADVERTISING, BEFORE COGS</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>7039879.86</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>the landed cost of the goods still has to come off</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>08. BOTTOM LINE</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>add back TDS withheld (recoverable in your ITR)</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>11592.94</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>reduces the cash Amazon sends, but it is not a cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>09. COST OF GOODS</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Landed cost of units shipped</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>-6200575.15</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>4133 units at Rs 1,500 average (96% priced from the Nexlev master, rest at that average)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>09. COST OF GOODS</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>less stock recovered from returns</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>453256.55</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>567 refunds, 61% came back sellable, valued at 88% (repack + restarted storage clock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>09. COST OF GOODS</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>NET COST OF GOODS</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>-5747318.6</v>
+      </c>
+      <c r="D74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>10. PROFIT</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>AMAZON CHANNEL CONTRIBUTION</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1304154.2</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>11.2% of sales - before company overhead, interest and tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>10. PROFIT</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>less business overhead</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>-581064.39</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>5% of sales - the rate your own margin master uses</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>10. PROFIT</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>less cost of finance</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>-348638.63</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>3% of sales - working capital tied up in stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>10. PROFIT</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PROFIT BEFORE TAX</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>374451.18</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>3.2% of sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>10. PROFIT</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>less income tax provision</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>-94241.87</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>25.17% under section 115BAA</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>10. PROFIT</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PROFIT AFTER TAX</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>280209.31</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2.4% of sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>12. COMPLETENESS</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Event lists Amazon returned with data</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>6</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AdjustmentEventList, AffordabilityExpenseEventList, AffordabilityExpenseReversalEventList, RefundEventList, ServiceFeeEventList, ShipmentEventList</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>12. COMPLETENESS</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
           <t>Event lists returned EMPTY</t>
         </is>
       </c>
-      <c r="C69" t="n">
+      <c r="C82" t="n">
         <v>27</v>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>incl. ShipmentSettleEventList - must stay empty or revenue double-counts</t>
         </is>

--- a/data/processed/reconciliation_NEXLEV_2026-08.xlsx
+++ b/data/processed/reconciliation_NEXLEV_2026-08.xlsx
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4133</v>
+        <v>3715</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -693,11 +693,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-596204.52</v>
+        <v>-537860.52</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -809,11 +809,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-153674.29</v>
+        <v>-130274.96</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -841,11 +841,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>-1364759.55</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>9707251.27</v>
+        <v>9730650.6</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1165772.75</v>
+        <v>-1195278.92</v>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
@@ -983,11 +983,11 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>8541478.52</v>
+        <v>8535371.68</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1003,11 +1003,11 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>8541478.52</v>
+        <v>7170612.13</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1023,11 +1023,11 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-5747318.6</v>
+        <v>-5433194.95</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1043,11 +1043,11 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1304154.2</v>
+        <v>1749010.13</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1079,11 +1079,11 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>374451.18</v>
+        <v>819307.11</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>280209.31</v>
+        <v>613103.89</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
@@ -1159,18 +1159,16 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Settlement cycles tied to Amazon's own totals</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>12 of 12</t>
-        </is>
+          <t xml:space="preserve">  Money in Amazon's events we could not classify</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>each cycle matches to the paisa</t>
+          <t>measured leaf-by-leaf against the payload, not asserted</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1329,11 +1327,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4133</v>
+        <v>3715</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>financial basis; differs from 4131 by cross-month timing</t>
+          <t>financial basis, Amazon.in only; the 416 gap to the line above is orders shipped across the month boundary</t>
         </is>
       </c>
     </row>
@@ -1345,15 +1343,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Product sales (GST NOT included)</t>
+          <t>Units shipped for other channels (MCF)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11621287.74</v>
+        <v>418</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>P&amp;L revenue</t>
+          <t>Amazon shipped these from our FBA stock but the sale was elsewhere - no revenue here, so no cost here either</t>
         </is>
       </c>
     </row>
@@ -1365,27 +1363,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shipping and gift wrap collected</t>
+          <t>Product sales (GST NOT included)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>66766.37</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+        <v>11621287.74</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>P&amp;L revenue</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02. RETURNS</t>
+          <t>01. SALES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Units refunded</t>
+          <t>Shipping and gift wrap collected</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>567</v>
+        <v>66766.37</v>
       </c>
       <c r="D11" t="inlineStr"/>
     </row>
@@ -1397,17 +1399,13 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Return rate % (in-month, mixed cohorts)</t>
+          <t>Units refunded</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13.72</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>these refunds mostly belong to earlier months' shipments</t>
-        </is>
-      </c>
+        <v>567</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1417,13 +1415,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sale value refunded (GST NOT included)</t>
+          <t>Return rate % (in-month, mixed cohorts)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-1753159.5</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
+        <v>15.26</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>on Amazon-only units; these refunds mostly belong to earlier months</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1433,17 +1435,13 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Commission on refunds (ex-GST)</t>
+          <t>Sale value refunded (GST NOT included)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>125100.29</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>given back to us</t>
-        </is>
-      </c>
+        <v>-1753159.5</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1453,11 +1451,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FixedClosingFee on refunds (ex-GST)</t>
+          <t>Commission on refunds (ex-GST)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12623</v>
+        <v>125100.29</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1473,11 +1471,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GiftwrapChargeback on refunds (ex-GST)</t>
+          <t>FixedClosingFee on refunds (ex-GST)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25.42</v>
+        <v>12623</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1493,15 +1491,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RefundCommission on refunds (ex-GST)</t>
+          <t>GiftwrapChargeback on refunds (ex-GST)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-31750</v>
+        <v>25.42</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Amazon kept this</t>
+          <t>given back to us</t>
         </is>
       </c>
     </row>
@@ -1513,33 +1511,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ShippingChargeback on refunds (ex-GST)</t>
+          <t>RefundCommission on refunds (ex-GST)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>870.34</v>
+        <v>-31750</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>given back to us</t>
+          <t>Amazon kept this</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>03. AMAZON FEES (ex-GST)</t>
+          <t>02. RETURNS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Commission (referral)</t>
+          <t>ShippingChargeback on refunds (ex-GST)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-826239.8100000001</v>
-      </c>
-      <c r="D19" t="inlineStr"/>
+        <v>870.34</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>given back to us</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1549,11 +1551,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FBA fulfilment</t>
+          <t>Commission (referral)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-596204.52</v>
+        <v>-826239.8100000001</v>
       </c>
       <c r="D20" t="inlineStr"/>
     </row>
@@ -1565,11 +1567,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Closing fee</t>
+          <t>FBA fulfilment</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-177166</v>
+        <v>-537860.52</v>
       </c>
       <c r="D21" t="inlineStr"/>
     </row>
@@ -1581,11 +1583,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Other selling fees</t>
+          <t>Closing fee</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-4586.44</v>
+        <v>-177166</v>
       </c>
       <c r="D22" t="inlineStr"/>
     </row>
@@ -1597,17 +1599,13 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FBAStorageFee</t>
+          <t>Other selling fees</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-111891.38</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>FBA Inventory Storage Fee</t>
-        </is>
-      </c>
+        <v>-4586.44</v>
+      </c>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1617,15 +1615,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FBALongTermStorageFee</t>
+          <t>FBAStorageFee</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-18510.93</v>
+        <v>-111891.38</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FBA Long Term Storage Fee</t>
+          <t>FBA Inventory Storage Fee</t>
         </is>
       </c>
     </row>
@@ -1637,15 +1635,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FBARemovalFee</t>
+          <t>FBALongTermStorageFee</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-9320</v>
+        <v>-18510.93</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FBA Removal Order: Return Fee</t>
+          <t>FBA Long Term Storage Fee</t>
         </is>
       </c>
     </row>
@@ -1657,15 +1655,15 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MFNPostageFee</t>
+          <t>FBARemovalFee</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-1199</v>
+        <v>-9320</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ServiceFee</t>
+          <t>FBA Removal Order: Return Fee</t>
         </is>
       </c>
     </row>
@@ -1677,15 +1675,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TechnologyFee</t>
+          <t>MFNPostageFee</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>-1199</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>RefusedDelivery</t>
+          <t>ServiceFee</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1703,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ShippingAddressUndeliverable</t>
+          <t>RefusedDelivery</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1723,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>UnableToDeliver</t>
+          <t>ShippingAddressUndeliverable</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1735,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Subscription</t>
+          <t>TechnologyFee</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1745,7 +1743,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ServiceFee</t>
+          <t>UnableToDeliver</t>
         </is>
       </c>
     </row>
@@ -1757,15 +1755,15 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FBAPerUnitFulfillmentFee</t>
+          <t>Subscription</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>204.36</v>
+        <v>0</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>UnableToDeliver</t>
+          <t>ServiceFee</t>
         </is>
       </c>
     </row>
@@ -1777,11 +1775,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FBAWeightBasedFee</t>
+          <t>FBAPerUnitFulfillmentFee</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1001</v>
+        <v>204.36</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1797,15 +1795,15 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FBAPerUnitFulfillmentFee</t>
+          <t>FBAWeightBasedFee</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1639.65</v>
+        <v>1001</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ShippingAddressUndeliverable</t>
+          <t>UnableToDeliver</t>
         </is>
       </c>
     </row>
@@ -1821,11 +1819,11 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4343.62</v>
+        <v>1639.65</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>RefusedDelivery</t>
+          <t>ShippingAddressUndeliverable</t>
         </is>
       </c>
     </row>
@@ -1837,15 +1835,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FBAWeightBasedFee</t>
+          <t>FBAPerUnitFulfillmentFee</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7577</v>
+        <v>4343.62</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ShippingAddressUndeliverable</t>
+          <t>RefusedDelivery</t>
         </is>
       </c>
     </row>
@@ -1861,45 +1859,53 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>18695</v>
+        <v>7577</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>RefusedDelivery</t>
+          <t>ShippingAddressUndeliverable</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>04. WE FUNDED</t>
+          <t>03. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Coupons / promotions</t>
+          <t>FBAWeightBasedFee</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-153674.29</v>
-      </c>
-      <c r="D37" t="inlineStr"/>
+        <v>18695</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>RefusedDelivery</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>04. WE FUNDED</t>
+          <t>03. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>No-cost EMI / bank offers</t>
+          <t>Multi-Channel Fulfilment (other channels)</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-69514.82000000001</v>
-      </c>
-      <c r="D38" t="inlineStr"/>
+        <v>-58344</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>418 units Amazon shipped for orders placed elsewhere - real cash, but it belongs to that channel, not to Amazon 3P</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1909,17 +1915,13 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Advertising (billed with GST)</t>
+          <t>Coupons / promotions</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-1501598.67</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>what Amazon Ads actually charged us, GST included</t>
-        </is>
-      </c>
+        <v>-130274.96</v>
+      </c>
+      <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1929,17 +1931,13 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  of which GST we get back as credit</t>
+          <t>No-cost EMI / bank offers</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>229057.42</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>reclaimed below - the real cost of ads is the ex-GST figure</t>
-        </is>
-      </c>
+        <v>-69514.82000000001</v>
+      </c>
+      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1949,55 +1947,55 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  real cost of advertising (ex-GST)</t>
+          <t>Advertising (billed with GST)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-1272541.24</v>
+        <v>-1364759.55</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>11.0% of sales</t>
+          <t>what Amazon Ads actually charged us, GST included</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05. CREDITS</t>
+          <t>04. WE FUNDED</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Reversal Reimbursement</t>
+          <t xml:space="preserve">  of which GST we get back as credit</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>101864.35</v>
+        <v>208183.66</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>compensation - no GST</t>
+          <t>reclaimed below - the real cost of ads is the ex-GST figure</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05. CREDITS</t>
+          <t>04. WE FUNDED</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Free Replacement Refund Items</t>
+          <t xml:space="preserve">  real cost of advertising (ex-GST)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>42851.01</v>
+        <v>-1156575.89</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>compensation - no GST</t>
+          <t>10.0% of sales</t>
         </is>
       </c>
     </row>
@@ -2009,11 +2007,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lostordamagedreimbursement</t>
+          <t>Reversal Reimbursement</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1114.52</v>
+        <v>101864.35</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2029,11 +2027,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Warehouse Damage</t>
+          <t>Free Replacement Refund Items</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1821.61</v>
+        <v>42851.01</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2049,15 +2047,15 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Commissioncorrection</t>
+          <t>Lostordamagedreimbursement</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>65468.13</v>
+        <v>1114.52</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>fee credit - carries GST, reverses ITC</t>
+          <t>compensation - no GST</t>
         </is>
       </c>
     </row>
@@ -2069,11 +2067,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Payment Retraction Items</t>
+          <t>Warehouse Damage</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-2230.36</v>
+        <v>1821.61</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2084,38 +2082,42 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06. GST AND TAX (not profit)</t>
+          <t>05. CREDITS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Output GST collected from customers</t>
+          <t>Commissioncorrection</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2062051.32</v>
+        <v>65468.13</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>held in trust - never ours</t>
+          <t>fee credit - carries GST, reverses ITC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06. GST AND TAX (not profit)</t>
+          <t>05. CREDITS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Output GST reversed on refunds</t>
+          <t>Payment Retraction Items</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-310107.66</v>
-      </c>
-      <c r="D49" t="inlineStr"/>
+        <v>-2230.36</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>compensation - no GST</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2125,15 +2127,15 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ITC on Amazon fees (reclaimable)</t>
+          <t>Output GST collected from customers</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>308098.34</v>
+        <v>2062051.32</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tie to Amazon's tax invoice AND GSTR-2B</t>
+          <t>held in trust - never ours</t>
         </is>
       </c>
     </row>
@@ -2145,17 +2147,13 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ITC on advertising (reclaimable)</t>
+          <t>Output GST reversed on refunds</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>229057.42</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>ad invoices carry GST too - claim it in GSTR-2B or you pay 18% twice</t>
-        </is>
-      </c>
+        <v>-310107.66</v>
+      </c>
+      <c r="D51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2165,15 +2163,15 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TCS withheld u/s 52 (0.5% of net sales)</t>
+          <t>ITC on Amazon fees (reclaimable)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-49015.15</v>
+        <v>288861.91</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PREPAYMENT ASSET - accept monthly in the GST portal or it is stranded</t>
+          <t>tie to Amazon's tax invoice AND GSTR-2B</t>
         </is>
       </c>
     </row>
@@ -2185,15 +2183,15 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TDS withheld u/s 194-O (0.1% of gross)</t>
+          <t>ITC on no-cost EMI (reclaimable)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-11592.94</v>
+        <v>10604.02</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>RECOVERABLE in ITR - charged on gross, so returns are a permanent drag</t>
+          <t>the EMI expense Amazon bills carries GST as well</t>
         </is>
       </c>
     </row>
@@ -2205,67 +2203,71 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Net GST still to remit in cash</t>
+          <t>ITC on advertising (reclaimable)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-1165772.75</v>
-      </c>
-      <c r="D54" t="inlineStr"/>
+        <v>208183.66</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ad invoices carry GST too - claim it in GSTR-2B or you pay 18% twice</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07. HOW THE TOTAL IS BUILT</t>
+          <t>06. GST AND TAX (not profit)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Product sales (GST not included)</t>
+          <t>TCS withheld u/s 52 (0.5% of net sales)</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>11621287.74</v>
+        <v>-49015.15</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>what we sold</t>
+          <t>PREPAYMENT ASSET - accept monthly in the GST portal or it is stranded</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07. HOW THE TOTAL IS BUILT</t>
+          <t>06. GST AND TAX (not profit)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>plus GST collected from customers</t>
+          <t>TDS withheld u/s 194-O (0.1% of gross)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2062051.32</v>
+        <v>-11592.94</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>comes in with the sale, goes out to the government</t>
+          <t>RECOVERABLE in ITR - charged on gross, so returns are a permanent drag</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07. HOW THE TOTAL IS BUILT</t>
+          <t>06. GST AND TAX (not profit)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>plus shipping and gift wrap</t>
+          <t>Net GST still to remit in cash</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>66766.37</v>
+        <v>-1195278.92</v>
       </c>
       <c r="D57" t="inlineStr"/>
     </row>
@@ -2277,15 +2279,15 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>less refunds to customers</t>
+          <t>Product sales (GST not included)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-2076295.91</v>
+        <v>11621287.74</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>sale value + GST returned</t>
+          <t>what we sold</t>
         </is>
       </c>
     </row>
@@ -2297,15 +2299,15 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>plus fees Amazon returned on refunds</t>
+          <t>plus GST collected from customers</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>126105.48</v>
+        <v>2062051.32</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>commission and closing come back; FBA fee does not</t>
+          <t>comes in with the sale, goes out to the government</t>
         </is>
       </c>
     </row>
@@ -2317,17 +2319,13 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>less Amazon fees (including GST on fees)</t>
+          <t>plus shipping and gift wrap</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-2019755.79</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>commission, FBA, closing, storage, removals</t>
-        </is>
-      </c>
+        <v>66766.37</v>
+      </c>
+      <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2337,13 +2335,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>less coupons and promotions</t>
+          <t>less refunds to customers</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-153674.29</v>
-      </c>
-      <c r="D61" t="inlineStr"/>
+        <v>-2076295.91</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>sale value + GST returned</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2353,13 +2355,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>less no-cost EMI and bank offers</t>
+          <t>plus fees Amazon returned on refunds</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-69514.82000000001</v>
-      </c>
-      <c r="D62" t="inlineStr"/>
+        <v>126105.48</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>commission and closing come back; FBA fee does not</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2369,13 +2375,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>plus reimbursements and corrections</t>
+          <t>less Amazon fees (including GST on fees)</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>210889.26</v>
-      </c>
-      <c r="D63" t="inlineStr"/>
+        <v>-2019755.79</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>commission, FBA, closing, storage, removals</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2385,17 +2395,13 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>less TCS withheld</t>
+          <t>less coupons and promotions</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-49015.15</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>you reclaim this in GST</t>
-        </is>
-      </c>
+        <v>-130274.96</v>
+      </c>
+      <c r="D64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2405,75 +2411,67 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>less TDS withheld</t>
+          <t>less no-cost EMI and bank offers</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-11592.94</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>you reclaim this in your ITR</t>
-        </is>
-      </c>
+        <v>-69514.82000000001</v>
+      </c>
+      <c r="D65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08. BOTTOM LINE</t>
+          <t>07. HOW THE TOTAL IS BUILT</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AMAZON SHOULD PAY US</t>
+          <t>plus reimbursements and corrections</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>9707251.27</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>add up everything above - this is the settlement</t>
-        </is>
-      </c>
+        <v>210889.26</v>
+      </c>
+      <c r="D66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08. BOTTOM LINE</t>
+          <t>07. HOW THE TOTAL IS BUILT</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>less GST we owe the government</t>
+          <t>less TCS withheld</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-1165772.75</v>
+        <v>-49015.15</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>output GST, less refunds, less credit on fee GST and ad GST, less TCS withheld</t>
+          <t>you reclaim this in GST</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08. BOTTOM LINE</t>
+          <t>07. HOW THE TOTAL IS BUILT</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MARKETPLACE CONTRIBUTION BEFORE COGS</t>
+          <t>less TDS withheld</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>8541478.52</v>
+        <v>-11592.94</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>what the marketplace actually left us</t>
+          <t>you reclaim this in your ITR</t>
         </is>
       </c>
     </row>
@@ -2485,15 +2483,15 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>less advertising (GST-inclusive cash)</t>
+          <t>AMAZON SHOULD PAY US</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-1501598.67</v>
+        <v>9730650.6</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>billed separately by Amazon Ads; its GST is credited back in the line above</t>
+          <t>add up everything above - this is the settlement</t>
         </is>
       </c>
     </row>
@@ -2505,15 +2503,15 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AFTER ADVERTISING, BEFORE COGS</t>
+          <t>less GST we owe the government</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>7039879.86</v>
+        <v>-1195278.92</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>the landed cost of the goods still has to come off</t>
+          <t>output GST, less refunds, less credit on fee GST and ad GST, less TCS withheld</t>
         </is>
       </c>
     </row>
@@ -2525,133 +2523,133 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>add back TDS withheld (recoverable in your ITR)</t>
+          <t>MARKETPLACE CONTRIBUTION BEFORE COGS</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>11592.94</v>
+        <v>8535371.68</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>reduces the cash Amazon sends, but it is not a cost</t>
+          <t>what the marketplace actually left us</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09. COST OF GOODS</t>
+          <t>08. BOTTOM LINE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Landed cost of units shipped</t>
+          <t>less advertising (GST-inclusive cash)</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-6200575.15</v>
+        <v>-1364759.55</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>4133 units at Rs 1,500 average (96% priced from the Nexlev master, rest at that average)</t>
+          <t>billed separately by Amazon Ads; its GST is credited back in the line above</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09. COST OF GOODS</t>
+          <t>08. BOTTOM LINE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>less stock recovered from returns</t>
+          <t>AFTER ADVERTISING, BEFORE COGS</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>453256.55</v>
+        <v>7170612.13</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>567 refunds, 61% came back sellable, valued at 88% (repack + restarted storage clock)</t>
+          <t>the landed cost of the goods still has to come off</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09. COST OF GOODS</t>
+          <t>08. BOTTOM LINE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NET COST OF GOODS</t>
+          <t>add back TDS withheld (recoverable in your ITR)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-5747318.6</v>
-      </c>
-      <c r="D74" t="inlineStr"/>
+        <v>11592.94</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>reduces the cash Amazon sends, but it is not a cost</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10. PROFIT</t>
+          <t>09. COST OF GOODS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AMAZON CHANNEL CONTRIBUTION</t>
+          <t>Landed cost of units shipped</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1304154.2</v>
+        <v>-5914157.89</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>11.2% of sales - before company overhead, interest and tax</t>
+          <t>3715 units at Rs 1,592 average (96% priced from the Nexlev master, rest at that average)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10. PROFIT</t>
+          <t>09. COST OF GOODS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>less business overhead</t>
+          <t>less stock recovered from returns</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-581064.39</v>
+        <v>480962.94</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>5% of sales - the rate your own margin master uses</t>
+          <t>567 refunds, 61% came back sellable, valued at 88% (repack + restarted storage clock)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10. PROFIT</t>
+          <t>09. COST OF GOODS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>less cost of finance</t>
+          <t>NET COST OF GOODS</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-348638.63</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>3% of sales - working capital tied up in stock</t>
-        </is>
-      </c>
+        <v>-5433194.95</v>
+      </c>
+      <c r="D77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2661,15 +2659,15 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PROFIT BEFORE TAX</t>
+          <t>AMAZON CHANNEL CONTRIBUTION</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>374451.18</v>
+        <v>1749010.13</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>3.2% of sales</t>
+          <t>15.1% of sales - before company overhead, interest and tax</t>
         </is>
       </c>
     </row>
@@ -2681,15 +2679,15 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>less income tax provision</t>
+          <t>less business overhead</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-94241.87</v>
+        <v>-581064.39</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>25.17% under section 115BAA</t>
+          <t>5% of sales - the rate your own margin master uses</t>
         </is>
       </c>
     </row>
@@ -2701,55 +2699,155 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PROFIT AFTER TAX</t>
+          <t>less cost of finance</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>280209.31</v>
+        <v>-348638.63</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2.4% of sales</t>
+          <t>3% of sales - working capital tied up in stock</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>12. COMPLETENESS</t>
+          <t>10. PROFIT</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Event lists Amazon returned with data</t>
+          <t>PROFIT BEFORE TAX</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>6</v>
+        <v>819307.11</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>AdjustmentEventList, AffordabilityExpenseEventList, AffordabilityExpenseReversalEventList, RefundEventList, ServiceFeeEventList, ShipmentEventList</t>
+          <t>7.1% of sales</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>10. PROFIT</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>less income tax provision</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>-206203.21</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>25.17% under section 115BAA</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>10. PROFIT</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>PROFIT AFTER TAX</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>613103.89</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>5.3% of sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>12. COMPLETENESS</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Event lists Amazon returned with data</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>6</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>AdjustmentEventList, AffordabilityExpenseEventList, AffordabilityExpenseReversalEventList, RefundEventList, ServiceFeeEventList, ShipmentEventList</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>12. COMPLETENESS</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
         <is>
           <t>Event lists returned EMPTY</t>
         </is>
       </c>
-      <c r="C82" t="n">
-        <v>27</v>
-      </c>
-      <c r="D82" t="inlineStr">
+      <c r="C85" t="n">
+        <v>29</v>
+      </c>
+      <c r="D85" t="inlineStr">
         <is>
           <t>incl. ShipmentSettleEventList - must stay empty or revenue double-counts</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>12. COMPLETENESS</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Money in ShipmentEventList we did not classify</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>MUST BE ZERO - this is measured, not asserted</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>12. COMPLETENESS</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Money in RefundEventList we did not classify</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>MUST BE ZERO - this is measured, not asserted</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2812,97 +2910,97 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FBAPerUnitFulfillmentFee</t>
+          <t>SERVICE:FBA Inventory Storage Fee|FBAStorageFee</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-182670.4499999935</v>
+        <v>-132031.83</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SERVICE:FBA Inventory Storage Fee|FBAStorageFee</t>
+          <t>FBAPerUnitFulfillmentFee</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-132031.83</v>
+        <v>-113824.5299999985</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>REFUND:RefundCommission</t>
+          <t>MCF:FBAPerUnitFulfillmentFee</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-37464.99999999999</v>
+        <v>-68845.9200000002</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SERVICE:FBA Long Term Storage Fee|FBALongTermStorageFee</t>
+          <t>REFUND:RefundCommission</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-21842.9</v>
+        <v>-37464.99999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SERVICE:FBA Removal Order: Return Fee|FBARemovalFee</t>
+          <t>SERVICE:FBA Long Term Storage Fee|FBALongTermStorageFee</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-10997.6</v>
+        <v>-21842.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ShippingChargeback</t>
+          <t>SERVICE:FBA Removal Order: Return Fee|FBARemovalFee</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-5292</v>
+        <v>-10997.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SERVICE:ServiceFee|MFNPostageFee</t>
+          <t>ShippingChargeback</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-1414.82</v>
+        <v>-5292</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GiftwrapChargeback</t>
+          <t>SERVICE:ServiceFee|MFNPostageFee</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-120</v>
+        <v>-1414.82</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TechnologyFee</t>
+          <t>GiftwrapChargeback</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>-120</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VariableClosingFee</t>
+          <t>TechnologyFee</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2912,7 +3010,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>REFUND:VariableClosingFee</t>
+          <t>VariableClosingFee</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2922,7 +3020,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SERVICE:RefusedDelivery|TechnologyFee</t>
+          <t>REFUND:VariableClosingFee</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2932,7 +3030,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SERVICE:ShippingAddressUndeliverable|TechnologyFee</t>
+          <t>SERVICE:RefusedDelivery|TechnologyFee</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2942,7 +3040,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GiftwrapCommission</t>
+          <t>SERVICE:ShippingAddressUndeliverable|TechnologyFee</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2952,7 +3050,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ShippingHB</t>
+          <t>GiftwrapCommission</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2962,7 +3060,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SERVICE:UnableToDeliver|TechnologyFee</t>
+          <t>ShippingHB</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2972,7 +3070,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>REFUND:GiftwrapCommission</t>
+          <t>SERVICE:UnableToDeliver|TechnologyFee</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2982,7 +3080,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>REFUND:ShippingHB</t>
+          <t>REFUND:GiftwrapCommission</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2992,7 +3090,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SERVICE:ServiceFee|Subscription</t>
+          <t>REFUND:ShippingHB</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -3002,100 +3100,110 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>REFUND:GiftwrapChargeback</t>
+          <t>SERVICE:ServiceFee|Subscription</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SERVICE:UnableToDeliver|FBAPerUnitFulfillmentFee</t>
+          <t>REFUND:GiftwrapChargeback</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>241.14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>REFUND:ShippingChargeback</t>
+          <t>SERVICE:UnableToDeliver|FBAPerUnitFulfillmentFee</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1027</v>
+        <v>241.14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SERVICE:UnableToDeliver|FBAWeightBasedFee</t>
+          <t>REFUND:ShippingChargeback</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1181.18</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SERVICE:ShippingAddressUndeliverable|FBAPerUnitFulfillmentFee</t>
+          <t>SERVICE:UnableToDeliver|FBAWeightBasedFee</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1934.789999999998</v>
+        <v>1181.18</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SERVICE:RefusedDelivery|FBAPerUnitFulfillmentFee</t>
+          <t>SERVICE:ShippingAddressUndeliverable|FBAPerUnitFulfillmentFee</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5125.470000000008</v>
+        <v>1934.789999999998</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SERVICE:ShippingAddressUndeliverable|FBAWeightBasedFee</t>
+          <t>SERVICE:RefusedDelivery|FBAPerUnitFulfillmentFee</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>8940.860000000001</v>
+        <v>5125.470000000008</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>REFUND:FixedClosingFee</t>
+          <t>SERVICE:ShippingAddressUndeliverable|FBAWeightBasedFee</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>14895.14000000005</v>
+        <v>8940.860000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SERVICE:RefusedDelivery|FBAWeightBasedFee</t>
+          <t>REFUND:FixedClosingFee</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>22060.09999999998</v>
+        <v>14895.14000000005</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>SERVICE:RefusedDelivery|FBAWeightBasedFee</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>22060.09999999998</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>REFUND:Commission</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B34" t="n">
         <v>147618.3400000001</v>
       </c>
     </row>

--- a/data/processed/reconciliation_NEXLEV_2026-08.xlsx
+++ b/data/processed/reconciliation_NEXLEV_2026-08.xlsx
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-929703.02</v>
+        <v>-473132.63</v>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
@@ -1079,11 +1079,11 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>819307.11</v>
+        <v>1275877.49</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>613103.89</v>
+        <v>954764.65</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2683,11 +2683,11 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-581064.39</v>
+        <v>-295707.89</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>5% of sales - the rate your own margin master uses</t>
+          <t>5% of landed cost - same basis as the margin calculator</t>
         </is>
       </c>
     </row>
@@ -2703,11 +2703,11 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-348638.63</v>
+        <v>-177424.74</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>3% of sales - working capital tied up in stock</t>
+          <t>3% of landed cost - working capital tied up in stock</t>
         </is>
       </c>
     </row>
@@ -2723,11 +2723,11 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>819307.11</v>
+        <v>1275877.49</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>7.1% of sales</t>
+          <t>11.0% of sales</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-206203.21</v>
+        <v>-321112.85</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -2763,11 +2763,11 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>613103.89</v>
+        <v>954764.65</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>5.3% of sales</t>
+          <t>8.2% of sales</t>
         </is>
       </c>
     </row>

--- a/data/processed/reconciliation_NEXLEV_2026-08.xlsx
+++ b/data/processed/reconciliation_NEXLEV_2026-08.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fee detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unmapped SKUs" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1043,11 +1044,11 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1749010.13</v>
+        <v>1807354.13</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1079,11 +1080,11 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1275877.49</v>
+        <v>1334221.49</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1095,11 +1096,11 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>954764.65</v>
+        <v>998424.63</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1168,7 +1169,103 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>measured leaf-by-leaf against the payload, not asserted</t>
+          <t>measured leaf-by-leaf across all 6 classified lists, not asserted</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Amazon sub-totals that disagree with our figure</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>every per-item breakdown re-added to the parent we booked</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>DOES IT MATCH THE BANK</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cash Amazon transferred this month</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>9136738.18</v>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>settlements whose transfer date landed in the month</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Accrual (what this month's events earned)</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>9730650.6</v>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>the figure everything above is built on</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Timing difference</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>593912.4199999999</v>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>settlement periods straddle month ends - timing, not error</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Settlements re-derived from their own events</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>10</v>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>opening balance + every event = the deposit Amazon states</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1451,15 +1548,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Commission on refunds (ex-GST)</t>
+          <t>Shipping and gift wrap refunded</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>125100.29</v>
+        <v>-13028.75</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>given back to us</t>
+          <t>returned to the customer along with the sale value</t>
         </is>
       </c>
     </row>
@@ -1471,11 +1568,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FixedClosingFee on refunds (ex-GST)</t>
+          <t>Commission on refunds (ex-GST)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>12623</v>
+        <v>125100.29</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1491,11 +1588,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GiftwrapChargeback on refunds (ex-GST)</t>
+          <t>FixedClosingFee on refunds (ex-GST)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25.42</v>
+        <v>12623</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1511,15 +1608,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RefundCommission on refunds (ex-GST)</t>
+          <t>GiftwrapChargeback on refunds (ex-GST)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-31750</v>
+        <v>25.42</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Amazon kept this</t>
+          <t>given back to us</t>
         </is>
       </c>
     </row>
@@ -1531,33 +1628,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ShippingChargeback on refunds (ex-GST)</t>
+          <t>RefundCommission on refunds (ex-GST)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>870.34</v>
+        <v>-31750</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>given back to us</t>
+          <t>Amazon kept this</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>03. AMAZON FEES (ex-GST)</t>
+          <t>02. RETURNS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Commission (referral)</t>
+          <t>ShippingChargeback on refunds (ex-GST)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-826239.8100000001</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
+        <v>870.34</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>given back to us</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1567,11 +1668,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FBA fulfilment</t>
+          <t>Commission (referral)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-537860.52</v>
+        <v>-826239.8100000001</v>
       </c>
       <c r="D21" t="inlineStr"/>
     </row>
@@ -1583,11 +1684,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Closing fee</t>
+          <t>FBA fulfilment</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-177166</v>
+        <v>-537860.52</v>
       </c>
       <c r="D22" t="inlineStr"/>
     </row>
@@ -1599,11 +1700,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Other selling fees</t>
+          <t>Closing fee</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-4586.44</v>
+        <v>-177166</v>
       </c>
       <c r="D23" t="inlineStr"/>
     </row>
@@ -1615,17 +1716,13 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FBAStorageFee</t>
+          <t>Other selling fees</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-111891.38</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>FBA Inventory Storage Fee</t>
-        </is>
-      </c>
+        <v>-4586.44</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1635,15 +1732,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FBALongTermStorageFee</t>
+          <t>FBAStorageFee</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-18510.93</v>
+        <v>-111891.38</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FBA Long Term Storage Fee</t>
+          <t>FBA Inventory Storage Fee</t>
         </is>
       </c>
     </row>
@@ -1655,15 +1752,15 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FBARemovalFee</t>
+          <t>FBALongTermStorageFee</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-9320</v>
+        <v>-18510.93</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FBA Removal Order: Return Fee</t>
+          <t>FBA Long Term Storage Fee</t>
         </is>
       </c>
     </row>
@@ -1675,15 +1772,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MFNPostageFee</t>
+          <t>FBARemovalFee</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-1199</v>
+        <v>-9320</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ServiceFee</t>
+          <t>FBA Removal Order: Return Fee</t>
         </is>
       </c>
     </row>
@@ -1695,15 +1792,15 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TechnologyFee</t>
+          <t>MFNPostageFee</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>-1199</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>RefusedDelivery</t>
+          <t>ServiceFee</t>
         </is>
       </c>
     </row>
@@ -1723,7 +1820,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ShippingAddressUndeliverable</t>
+          <t>RefusedDelivery</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1840,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>UnableToDeliver</t>
+          <t>ShippingAddressUndeliverable</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1852,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Subscription</t>
+          <t>TechnologyFee</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1763,7 +1860,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ServiceFee</t>
+          <t>UnableToDeliver</t>
         </is>
       </c>
     </row>
@@ -1775,15 +1872,15 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FBAPerUnitFulfillmentFee</t>
+          <t>Subscription</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>204.36</v>
+        <v>0</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>UnableToDeliver</t>
+          <t>ServiceFee</t>
         </is>
       </c>
     </row>
@@ -1795,11 +1892,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FBAWeightBasedFee</t>
+          <t>FBAPerUnitFulfillmentFee</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1001</v>
+        <v>204.36</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1815,15 +1912,15 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FBAPerUnitFulfillmentFee</t>
+          <t>FBAWeightBasedFee</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1639.65</v>
+        <v>1001</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ShippingAddressUndeliverable</t>
+          <t>UnableToDeliver</t>
         </is>
       </c>
     </row>
@@ -1839,11 +1936,11 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4343.62</v>
+        <v>1639.65</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>RefusedDelivery</t>
+          <t>ShippingAddressUndeliverable</t>
         </is>
       </c>
     </row>
@@ -1855,15 +1952,15 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FBAWeightBasedFee</t>
+          <t>FBAPerUnitFulfillmentFee</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>7577</v>
+        <v>4343.62</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ShippingAddressUndeliverable</t>
+          <t>RefusedDelivery</t>
         </is>
       </c>
     </row>
@@ -1879,11 +1976,11 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>18695</v>
+        <v>7577</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>RefusedDelivery</t>
+          <t>ShippingAddressUndeliverable</t>
         </is>
       </c>
     </row>
@@ -1895,33 +1992,37 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Multi-Channel Fulfilment (other channels)</t>
+          <t>FBAWeightBasedFee</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-58344</v>
+        <v>18695</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>418 units Amazon shipped for orders placed elsewhere - real cash, but it belongs to that channel, not to Amazon 3P</t>
+          <t>RefusedDelivery</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>04. WE FUNDED</t>
+          <t>03. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Coupons / promotions</t>
+          <t>Multi-Channel Fulfilment (other channels)</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-130274.96</v>
-      </c>
-      <c r="D39" t="inlineStr"/>
+        <v>-58344</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>418 units Amazon shipped for orders placed elsewhere - real cash, but it belongs to that channel, not to Amazon 3P</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1931,11 +2032,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>No-cost EMI / bank offers</t>
+          <t>Coupons / promotions</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-69514.82000000001</v>
+        <v>-130274.96</v>
       </c>
       <c r="D40" t="inlineStr"/>
     </row>
@@ -1947,15 +2048,15 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Advertising (billed with GST)</t>
+          <t xml:space="preserve">  of which PromotionMetaDataDefinitionValue</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-1364759.55</v>
+        <v>-130274.96</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>what Amazon Ads actually charged us, GST included</t>
+          <t>Amazon returns no real promotion type here, so this does NOT tell us whether coupons ran - the missing coupon-redemption fee stays an open question</t>
         </is>
       </c>
     </row>
@@ -1967,17 +2068,13 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">  of which GST we get back as credit</t>
+          <t>No-cost EMI / bank offers</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>208183.66</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>reclaimed below - the real cost of ads is the ex-GST figure</t>
-        </is>
-      </c>
+        <v>-69514.82000000001</v>
+      </c>
+      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1987,55 +2084,55 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">  real cost of advertising (ex-GST)</t>
+          <t>Advertising (billed with GST)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-1156575.89</v>
+        <v>-1364759.55</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10.0% of sales</t>
+          <t>what Amazon Ads actually charged us, GST included</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>05. CREDITS</t>
+          <t>04. WE FUNDED</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Reversal Reimbursement</t>
+          <t xml:space="preserve">  of which GST we get back as credit</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>101864.35</v>
+        <v>208183.66</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>compensation - no GST</t>
+          <t>reclaimed below - the real cost of ads is the ex-GST figure</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>05. CREDITS</t>
+          <t>04. WE FUNDED</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Free Replacement Refund Items</t>
+          <t xml:space="preserve">  real cost of advertising (ex-GST)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>42851.01</v>
+        <v>-1156575.89</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>compensation - no GST</t>
+          <t>10.0% of sales</t>
         </is>
       </c>
     </row>
@@ -2047,11 +2144,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lostordamagedreimbursement</t>
+          <t>Reversal Reimbursement</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1114.52</v>
+        <v>101864.35</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2067,11 +2164,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Warehouse Damage</t>
+          <t>Free Replacement Refund Items</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1821.61</v>
+        <v>42851.01</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2087,15 +2184,15 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Commissioncorrection</t>
+          <t>Lostordamagedreimbursement</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>65468.13</v>
+        <v>1114.52</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>fee credit - carries GST, reverses ITC</t>
+          <t>compensation - no GST</t>
         </is>
       </c>
     </row>
@@ -2107,11 +2204,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Payment Retraction Items</t>
+          <t>Warehouse Damage</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-2230.36</v>
+        <v>1821.61</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2122,38 +2219,42 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06. GST AND TAX (not profit)</t>
+          <t>05. CREDITS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Output GST collected from customers</t>
+          <t>Commissioncorrection</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2062051.32</v>
+        <v>65468.13</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>held in trust - never ours</t>
+          <t>fee credit - carries GST, reverses ITC</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06. GST AND TAX (not profit)</t>
+          <t>05. CREDITS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Output GST reversed on refunds</t>
+          <t>Payment Retraction Items</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-310107.66</v>
-      </c>
-      <c r="D51" t="inlineStr"/>
+        <v>-2230.36</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>compensation - no GST</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2163,15 +2264,15 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ITC on Amazon fees (reclaimable)</t>
+          <t>Output GST collected from customers</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>288861.91</v>
+        <v>2062051.32</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>tie to Amazon's tax invoice AND GSTR-2B</t>
+          <t>held in trust - never ours</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2284,13 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ITC on no-cost EMI (reclaimable)</t>
+          <t>Output GST reversed on refunds</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>10604.02</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>the EMI expense Amazon bills carries GST as well</t>
-        </is>
-      </c>
+        <v>-310107.66</v>
+      </c>
+      <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2203,15 +2300,15 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ITC on advertising (reclaimable)</t>
+          <t>ITC on Amazon fees (reclaimable)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>208183.66</v>
+        <v>288861.91</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ad invoices carry GST too - claim it in GSTR-2B or you pay 18% twice</t>
+          <t>tie to Amazon's tax invoice AND GSTR-2B</t>
         </is>
       </c>
     </row>
@@ -2223,15 +2320,15 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TCS withheld u/s 52 (0.5% of net sales)</t>
+          <t>ITC on no-cost EMI (reclaimable)</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-49015.15</v>
+        <v>10604.02</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PREPAYMENT ASSET - accept monthly in the GST portal or it is stranded</t>
+          <t>the EMI expense Amazon bills carries GST as well</t>
         </is>
       </c>
     </row>
@@ -2243,15 +2340,15 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TDS withheld u/s 194-O (0.1% of gross)</t>
+          <t>ITC on advertising (reclaimable)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-11592.94</v>
+        <v>208183.66</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>RECOVERABLE in ITR - charged on gross, so returns are a permanent drag</t>
+          <t>ad invoices carry GST too - claim it in GSTR-2B or you pay 18% twice</t>
         </is>
       </c>
     </row>
@@ -2263,51 +2360,55 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Net GST still to remit in cash</t>
+          <t>TCS withheld u/s 52 (0.5% of net sales)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-1195278.92</v>
-      </c>
-      <c r="D57" t="inlineStr"/>
+        <v>-49015.15</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>PREPAYMENT ASSET - accept monthly in the GST portal or it is stranded</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07. HOW THE TOTAL IS BUILT</t>
+          <t>06. GST AND TAX (not profit)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Product sales (GST not included)</t>
+          <t>TDS withheld u/s 194-O (0.1% of gross)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>11621287.74</v>
+        <v>-11592.94</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>what we sold</t>
+          <t>RECOVERABLE in ITR - charged on gross, so returns are a permanent drag</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07. HOW THE TOTAL IS BUILT</t>
+          <t>06. GST AND TAX (not profit)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>plus GST collected from customers</t>
+          <t>Net GST still to remit in cash</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2062051.32</v>
+        <v>-1195278.92</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>comes in with the sale, goes out to the government</t>
+          <t>marketplace GST only - import IGST paid at the bill of entry is also creditable and is NOT netted here</t>
         </is>
       </c>
     </row>
@@ -2319,13 +2420,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>plus shipping and gift wrap</t>
+          <t>Product sales (GST not included)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>66766.37</v>
-      </c>
-      <c r="D60" t="inlineStr"/>
+        <v>11621287.74</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>what we sold</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2335,15 +2440,15 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>less refunds to customers</t>
+          <t>plus GST collected from customers</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-2076295.91</v>
+        <v>2062051.32</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>sale value + GST returned</t>
+          <t>comes in with the sale, goes out to the government</t>
         </is>
       </c>
     </row>
@@ -2355,17 +2460,13 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>plus fees Amazon returned on refunds</t>
+          <t>plus shipping and gift wrap</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>126105.48</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>commission and closing come back; FBA fee does not</t>
-        </is>
-      </c>
+        <v>66766.37</v>
+      </c>
+      <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2375,15 +2476,15 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>less Amazon fees (including GST on fees)</t>
+          <t>less refunds to customers</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-2019755.79</v>
+        <v>-2076295.91</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>commission, FBA, closing, storage, removals</t>
+          <t>sale value + GST returned</t>
         </is>
       </c>
     </row>
@@ -2395,13 +2496,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>less coupons and promotions</t>
+          <t>plus fees Amazon returned on refunds</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-130274.96</v>
-      </c>
-      <c r="D64" t="inlineStr"/>
+        <v>126105.48</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>commission and closing come back; FBA fee does not</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2411,13 +2516,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>less no-cost EMI and bank offers</t>
+          <t>less Amazon fees (including GST on fees)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-69514.82000000001</v>
-      </c>
-      <c r="D65" t="inlineStr"/>
+        <v>-2019755.79</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>commission, FBA, closing, storage, removals</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2427,11 +2536,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>plus reimbursements and corrections</t>
+          <t>less coupons and promotions</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>210889.26</v>
+        <v>-130274.96</v>
       </c>
       <c r="D66" t="inlineStr"/>
     </row>
@@ -2443,17 +2552,13 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>less TCS withheld</t>
+          <t>less no-cost EMI and bank offers</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-49015.15</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>you reclaim this in GST</t>
-        </is>
-      </c>
+        <v>-69514.82000000001</v>
+      </c>
+      <c r="D67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2463,55 +2568,51 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>less TDS withheld</t>
+          <t>plus reimbursements and corrections</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-11592.94</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>you reclaim this in your ITR</t>
-        </is>
-      </c>
+        <v>210889.26</v>
+      </c>
+      <c r="D68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08. BOTTOM LINE</t>
+          <t>07. HOW THE TOTAL IS BUILT</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AMAZON SHOULD PAY US</t>
+          <t>less TCS withheld</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>9730650.6</v>
+        <v>-49015.15</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>add up everything above - this is the settlement</t>
+          <t>you reclaim this in GST</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08. BOTTOM LINE</t>
+          <t>07. HOW THE TOTAL IS BUILT</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>less GST we owe the government</t>
+          <t>less TDS withheld</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-1195278.92</v>
+        <v>-11592.94</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>output GST, less refunds, less credit on fee GST and ad GST, less TCS withheld</t>
+          <t>you reclaim this in your ITR</t>
         </is>
       </c>
     </row>
@@ -2523,15 +2624,15 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MARKETPLACE CONTRIBUTION BEFORE COGS</t>
+          <t>AMAZON SHOULD PAY US</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>8535371.68</v>
+        <v>9730650.6</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>what the marketplace actually left us</t>
+          <t>add up everything above - this is the settlement</t>
         </is>
       </c>
     </row>
@@ -2543,15 +2644,15 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>less advertising (GST-inclusive cash)</t>
+          <t>less GST we owe the government</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-1364759.55</v>
+        <v>-1195278.92</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>billed separately by Amazon Ads; its GST is credited back in the line above</t>
+          <t>output GST, less refunds, less credit on fee GST and ad GST, less TCS withheld</t>
         </is>
       </c>
     </row>
@@ -2563,15 +2664,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>AFTER ADVERTISING, BEFORE COGS</t>
+          <t>MARKETPLACE CONTRIBUTION BEFORE COGS</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>7170612.13</v>
+        <v>8535371.68</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>the landed cost of the goods still has to come off</t>
+          <t>what the marketplace actually left us</t>
         </is>
       </c>
     </row>
@@ -2583,173 +2684,173 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>add back TDS withheld (recoverable in your ITR)</t>
+          <t>less advertising (GST-inclusive cash)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>11592.94</v>
+        <v>-1364759.55</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>reduces the cash Amazon sends, but it is not a cost</t>
+          <t>billed separately by Amazon Ads; its GST is credited back in the line above</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09. COST OF GOODS</t>
+          <t>08. BOTTOM LINE</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Landed cost of units shipped</t>
+          <t>AFTER ADVERTISING, BEFORE COGS</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-5914157.89</v>
+        <v>7170612.13</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>3715 units at Rs 1,592 average (96% priced from the Nexlev master, rest at that average)</t>
+          <t>the landed cost of the goods still has to come off</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09. COST OF GOODS</t>
+          <t>08. BOTTOM LINE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>less stock recovered from returns</t>
+          <t>add back TDS withheld (recoverable in your ITR)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>480962.94</v>
+        <v>11592.94</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>567 refunds, 61% came back sellable, valued at 88% (repack + restarted storage clock)</t>
+          <t>reduces the cash Amazon sends, but it is not a cost</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09. COST OF GOODS</t>
+          <t>08. BOTTOM LINE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NET COST OF GOODS</t>
+          <t>add back Multi-Channel Fulfilment fee</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-5433194.95</v>
-      </c>
-      <c r="D77" t="inlineStr"/>
+        <v>58344</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>418 units Amazon shipped for orders placed on another channel - real cash, but that channel's cost, not Amazon's (ex-GST; the GST on it is already credited in the line above)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10. PROFIT</t>
+          <t>09. COST OF GOODS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>AMAZON CHANNEL CONTRIBUTION</t>
+          <t>Landed cost of units shipped</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1749010.13</v>
+        <v>-5914157.89</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>15.1% of sales - before company overhead, interest and tax</t>
+          <t>3715 units at Rs 1,592 average (96% priced from the Nexlev master, rest at that average)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10. PROFIT</t>
+          <t>09. COST OF GOODS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>less business overhead</t>
+          <t xml:space="preserve">  of which priced on an ASSUMPTION</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-295707.89</v>
+        <v>-210139.66</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>5% of landed cost - same basis as the margin calculator</t>
+          <t>132 units across 20 SKUs have no row in the Nexlev master - see the 'Unmapped SKUs' sheet; map them and this line becomes measured</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10. PROFIT</t>
+          <t>09. COST OF GOODS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>less cost of finance</t>
+          <t>less stock recovered from returns</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-177424.74</v>
+        <v>480962.94</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>3% of landed cost - working capital tied up in stock</t>
+          <t>567 refunds, 61% came back sellable, valued at 88% (repack + restarted storage clock)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10. PROFIT</t>
+          <t>09. COST OF GOODS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PROFIT BEFORE TAX</t>
+          <t>Inbound freight to FBA - NOT INCLUDED</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1275877.49</v>
+        <v>0</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>11.0% of sales</t>
+          <t>we self-ship into FBA, so this never appears in Amazon's data and it is not in the margin master either - profit below is overstated by it. Re-run with --freight-per-unit &lt;Rs&gt; to book it</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10. PROFIT</t>
+          <t>09. COST OF GOODS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>less income tax provision</t>
+          <t>NET COST OF GOODS</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-321112.85</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>25.17% under section 115BAA</t>
-        </is>
-      </c>
+        <v>-5433194.95</v>
+      </c>
+      <c r="D82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2759,95 +2860,695 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PROFIT AFTER TAX</t>
+          <t>AMAZON CHANNEL CONTRIBUTION</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>954764.65</v>
+        <v>1807354.13</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>8.2% of sales</t>
+          <t>15.6% of sales - before company overhead, interest and tax</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>12. COMPLETENESS</t>
+          <t>10. PROFIT</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Event lists Amazon returned with data</t>
+          <t>less business overhead</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>6</v>
+        <v>-295707.89</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>AdjustmentEventList, AffordabilityExpenseEventList, AffordabilityExpenseReversalEventList, RefundEventList, ServiceFeeEventList, ShipmentEventList</t>
+          <t>5% of landed cost - same basis as the margin calculator</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>12. COMPLETENESS</t>
+          <t>10. PROFIT</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Event lists returned EMPTY</t>
+          <t>less cost of finance</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>29</v>
+        <v>-177424.74</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>incl. ShipmentSettleEventList - must stay empty or revenue double-counts</t>
+          <t>3% of landed cost - working capital tied up in stock</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>12. COMPLETENESS</t>
+          <t>10. PROFIT</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Money in ShipmentEventList we did not classify</t>
+          <t>PROFIT BEFORE TAX</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-0</v>
+        <v>1334221.49</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>MUST BE ZERO - this is measured, not asserted</t>
+          <t>11.5% of sales</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>10. PROFIT</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>less income tax provision</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>-335796.87</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>25.17% under section 115BAA</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>10. PROFIT</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>PROFIT AFTER TAX</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>998424.63</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>8.6% of sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>12. COMPLETENESS</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Event lists Amazon returned with data</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>6</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdjustmentEventList, AffordabilityExpenseEventList, AffordabilityExpenseReversalEventList, RefundEventList, ServiceFeeEventList, ShipmentEventList</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>12. COMPLETENESS</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Event lists returned EMPTY</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>29</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>incl. ShipmentSettleEventList - must stay empty or revenue double-counts</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>12. COMPLETENESS</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Money in ShipmentEventList we did not classify</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>MUST BE ZERO - this is measured, not asserted</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>12. COMPLETENESS</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
         <is>
           <t>Money in RefundEventList we did not classify</t>
         </is>
       </c>
-      <c r="C87" t="n">
+      <c r="C92" t="n">
         <v>-0</v>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>MUST BE ZERO - this is measured, not asserted</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>12. COMPLETENESS</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Money in ServiceFeeEventList we did not classify</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>MUST BE ZERO - this is measured, not asserted</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>12. COMPLETENESS</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Money in AdjustmentEventList we did not classify</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>zero by construction - we book Amazon's parent total; the real test for this list is the breakdown check below</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>12. COMPLETENESS</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Money in AffordabilityExpenseEventList we did not classify</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>zero by construction - we book Amazon's parent total; the real test for this list is the breakdown check below</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>12. COMPLETENESS</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Money in AffordabilityExpenseReversalEventList we did not classify</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>zero by construction - we book Amazon's parent total; the real test for this list is the breakdown check below</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>12. COMPLETENESS</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Breakdowns that disagree with their parent</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>every AdjustmentItemList and Affordability base+GST re-added to the parent total we booked</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>13. BANK TIE-OUT</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Settlement 31/07/2026 - 07/08/2026  #EpyKFnvKPO0UseyGWOBhBsbWbtBrllFygs_m0sIQ7Rw</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1725070.29</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>closed, transferred 2026-08-07 to a/c ...008 - ties exactly: opening 0 + events 1,725,070 = 1,725,070</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>13. BANK TIE-OUT</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Settlement 31/07/2026 - 07/08/2026  #BYibnRovNZHg1P4a8L9B8K7gAVqzLkp9aSWIGiYT8a8</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>480833.4</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>closed, transferred 2026-08-07 to a/c ...008 - ties exactly: opening 0 + events 480,833 = 480,833</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>13. BANK TIE-OUT</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Settlement 07/08/2026 - 14/08/2026  #qi1SEXQFEWltMlJJ3u3-78uykuEVcNxBSFviVstqx40</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>1689832.41</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>closed, transferred 2026-08-14 to a/c ...008 - ties exactly: opening 0 + events 1,689,832 = 1,689,832</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>13. BANK TIE-OUT</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Settlement 07/08/2026 - 14/08/2026  #nbrNd14gFT6XF6hDagxzKzPV8ElXYzRIHo5IIVFV-SQ</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>559243.8199999999</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>closed, transferred 2026-08-14 to a/c ...008 - ties exactly: opening 0 + events 559,244 = 559,244</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>13. BANK TIE-OUT</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Settlement 14/08/2026 - 21/08/2026  #S9Fkp3FTRgkf6dWA_Qs-qndkx0jUBjHtywDnlAxTWOM</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>2093650.61</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>closed, transferred 2026-08-21 to a/c ...008 - ties exactly: opening 0 + events 2,093,651 = 2,093,651</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>13. BANK TIE-OUT</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Settlement 14/08/2026 - 21/08/2026  #pJVgmCSYEdE5Mhopb6W58kOcPUwryJ1XpO8-lk2bLnw</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>614959.29</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>closed, transferred 2026-08-21 to a/c ...008 - ties exactly: opening 0 + events 614,959 = 614,959</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>13. BANK TIE-OUT</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Settlement 21/08/2026 - 28/08/2026  #C61MFNpQJBP4bDB2LdFzKaqpFcCVxqsdOtDKxsfmc5w</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>1467714.36</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>closed, transferred 2026-08-28 to a/c ...008 - ties exactly: opening 0 + events 1,467,714 = 1,467,714</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>13. BANK TIE-OUT</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Settlement 21/08/2026 - 28/08/2026  #QNwQb0I2fYRMNherxVceFyNVbUB0pHXEzfw4YeavBJQ</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>505434</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>closed, transferred 2026-08-28 to a/c ...008 - ties exactly: opening 0 + events 505,434 = 505,434</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>13. BANK TIE-OUT</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Settlement 28/08/2026 - 04/09/2026  #-tQ1ArXEHgVJvSrggnUO2r5BK42DF-NRLJIHrGUtZ18</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>1088816.38</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>closed, transferred 2026-09-04 to a/c ...008 - ties exactly: opening 0 + events 1,088,816 = 1,088,816</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>13. BANK TIE-OUT</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Settlement 28/08/2026 - 04/09/2026  #vcTJvhcLLIZ7-2r7tcpy_gYTWS0BO6-A4zB8xOcrcyU</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>430360.71</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>closed, transferred 2026-09-04 to a/c ...008 - ties exactly: opening 0 + events 430,361 = 430,361</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>13. BANK TIE-OUT</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>CASH Amazon actually transferred this month</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>9136738.18</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>sum of settlements whose transfer date falls inside the month - this is what should appear on the bank statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>13. BANK TIE-OUT</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Accrual: what this month's events say we earned</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>9730650.6</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>section 08 - events POSTED in the month, whenever they get paid</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>13. BANK TIE-OUT</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Timing difference (accrual less cash)</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>593912.42</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>settlement periods straddle month ends - a difference here is TIMING, not error; it is only a problem if a group above fails to tie</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>13. BANK TIE-OUT</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Groups re-derived from their own events</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>10</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>10 of 10 tie to the rupee</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>14. RETURNS - COHORT VIEW (memo)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Return rate used above (in-month)</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>refunds POSTED this month over units shipped this month - two different populations, which is why this is only a proxy</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>14. RETURNS - COHORT VIEW (memo)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Returns already arrived from this month's orders</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>after 0 month(s); matured cohorts say that is only 67% of what a cohort ever returns</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>14. RETURNS - COHORT VIEW (memo)</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>EXPECTED LIFETIME return rate for this month's orders</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>grossed up on the curve from cohorts at least 3 months old (their lifetime rate: 15.60%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>14. RETURNS - COHORT VIEW (memo)</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Units this month's shipments will return</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>590</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>the cohort rate applied to the 3,715 units this P&amp;L is built on (the cohort itself is 4,131 units ordered in the month); vs 567 refunds actually posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>14. RETURNS - COHORT VIEW (memo)</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Net cost of one return</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>-2021.32</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Rs3,092 sale value given back, less Rs222 of fees returned, less Rs848 of stock that comes back sellable</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>14. RETURNS - COHORT VIEW (memo)</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>PROVISION if charged on a cohort basis</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>-47236.79</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>+23 more returns than the month booked. The bottom line above is NOT adjusted for this - it stays on the settlement basis that section 13 ties to the bank</t>
         </is>
       </c>
     </row>
@@ -3210,4 +3911,380 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>sku</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>asin</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>assumed_cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FBK80024</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>B0GLHC8CB3</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33431.30975741782</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FBA79773</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B0F74DJYG6</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3" t="n">
+        <v>31839.34262611221</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FBA79843</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>B0FMF1D9NV</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>13</v>
+      </c>
+      <c r="D4" t="n">
+        <v>20695.57270697294</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FBA79721</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>B0F2N4N83Y</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D5" t="n">
+        <v>14327.70418175049</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FBA80113</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>B0GYS6CJD9</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D6" t="n">
+        <v>14327.70418175049</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FBK79714</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>14327.70418175049</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FBK79591</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>B0F29SZCVF</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D8" t="n">
+        <v>14327.70418175049</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FBA79775</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>B0F67775SH</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>9</v>
+      </c>
+      <c r="D9" t="n">
+        <v>14327.70418175049</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FBA79771</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>B0F678L8YT</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="n">
+        <v>14327.70418175049</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FBA79698</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>B0DTK4FY1G</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7959.835656528053</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FBM79773</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6367.868525222442</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FBA79436</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>B0DGTGKPJR</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6367.868525222442</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FBA79606</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>B0F2N37819</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3183.934262611221</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FBK80015</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>B0GKNGWLJ2</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3183.934262611221</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FBA79778</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>B0F67BW7SF</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3183.934262611221</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FBA79777</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>B0F6795PDP</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1591.967131305611</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FBA79913</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>B0FYNLPK1B</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1591.967131305611</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FBM79263</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1591.967131305611</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FBM79436</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1591.967131305611</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FBM79992</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1591.967131305611</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/processed/reconciliation_NEXLEV_2026-08.xlsx
+++ b/data/processed/reconciliation_NEXLEV_2026-08.xlsx
@@ -3160,7 +3160,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Settlement 31/07/2026 - 07/08/2026  #EpyKFnvKPO0UseyGWOBhBsbWbtBrllFygs_m0sIQ7Rw</t>
+          <t>Settlement 31/07/2026 - 07/08/2026  #EpyKFnvK</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>closed, transferred 2026-08-07 to a/c ...008 - ties exactly: opening 0 + events 1,725,070 = 1,725,070</t>
+          <t>group EpyKFnvKPO0UseyGWOBhBsbWbtBrllFygs_m0sIQ7Rw - closed, transferred 2026-08-07 to a/c ...008 - ties exactly: opening 0 + events 1,725,070 = 1,725,070</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Settlement 31/07/2026 - 07/08/2026  #BYibnRovNZHg1P4a8L9B8K7gAVqzLkp9aSWIGiYT8a8</t>
+          <t>Settlement 31/07/2026 - 07/08/2026  #BYibnRov</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>closed, transferred 2026-08-07 to a/c ...008 - ties exactly: opening 0 + events 480,833 = 480,833</t>
+          <t>group BYibnRovNZHg1P4a8L9B8K7gAVqzLkp9aSWIGiYT8a8 - closed, transferred 2026-08-07 to a/c ...008 - ties exactly: opening 0 + events 480,833 = 480,833</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Settlement 07/08/2026 - 14/08/2026  #qi1SEXQFEWltMlJJ3u3-78uykuEVcNxBSFviVstqx40</t>
+          <t>Settlement 07/08/2026 - 14/08/2026  #qi1SEXQF</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>closed, transferred 2026-08-14 to a/c ...008 - ties exactly: opening 0 + events 1,689,832 = 1,689,832</t>
+          <t>group qi1SEXQFEWltMlJJ3u3-78uykuEVcNxBSFviVstqx40 - closed, transferred 2026-08-14 to a/c ...008 - ties exactly: opening 0 + events 1,689,832 = 1,689,832</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Settlement 07/08/2026 - 14/08/2026  #nbrNd14gFT6XF6hDagxzKzPV8ElXYzRIHo5IIVFV-SQ</t>
+          <t>Settlement 07/08/2026 - 14/08/2026  #nbrNd14g</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>closed, transferred 2026-08-14 to a/c ...008 - ties exactly: opening 0 + events 559,244 = 559,244</t>
+          <t>group nbrNd14gFT6XF6hDagxzKzPV8ElXYzRIHo5IIVFV-SQ - closed, transferred 2026-08-14 to a/c ...008 - ties exactly: opening 0 + events 559,244 = 559,244</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Settlement 14/08/2026 - 21/08/2026  #S9Fkp3FTRgkf6dWA_Qs-qndkx0jUBjHtywDnlAxTWOM</t>
+          <t>Settlement 14/08/2026 - 21/08/2026  #S9Fkp3FT</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>closed, transferred 2026-08-21 to a/c ...008 - ties exactly: opening 0 + events 2,093,651 = 2,093,651</t>
+          <t>group S9Fkp3FTRgkf6dWA_Qs-qndkx0jUBjHtywDnlAxTWOM - closed, transferred 2026-08-21 to a/c ...008 - ties exactly: opening 0 + events 2,093,651 = 2,093,651</t>
         </is>
       </c>
     </row>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Settlement 14/08/2026 - 21/08/2026  #pJVgmCSYEdE5Mhopb6W58kOcPUwryJ1XpO8-lk2bLnw</t>
+          <t>Settlement 14/08/2026 - 21/08/2026  #pJVgmCSY</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>closed, transferred 2026-08-21 to a/c ...008 - ties exactly: opening 0 + events 614,959 = 614,959</t>
+          <t>group pJVgmCSYEdE5Mhopb6W58kOcPUwryJ1XpO8-lk2bLnw - closed, transferred 2026-08-21 to a/c ...008 - ties exactly: opening 0 + events 614,959 = 614,959</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Settlement 21/08/2026 - 28/08/2026  #C61MFNpQJBP4bDB2LdFzKaqpFcCVxqsdOtDKxsfmc5w</t>
+          <t>Settlement 21/08/2026 - 28/08/2026  #C61MFNpQ</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>closed, transferred 2026-08-28 to a/c ...008 - ties exactly: opening 0 + events 1,467,714 = 1,467,714</t>
+          <t>group C61MFNpQJBP4bDB2LdFzKaqpFcCVxqsdOtDKxsfmc5w - closed, transferred 2026-08-28 to a/c ...008 - ties exactly: opening 0 + events 1,467,714 = 1,467,714</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Settlement 21/08/2026 - 28/08/2026  #QNwQb0I2fYRMNherxVceFyNVbUB0pHXEzfw4YeavBJQ</t>
+          <t>Settlement 21/08/2026 - 28/08/2026  #QNwQb0I2</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>closed, transferred 2026-08-28 to a/c ...008 - ties exactly: opening 0 + events 505,434 = 505,434</t>
+          <t>group QNwQb0I2fYRMNherxVceFyNVbUB0pHXEzfw4YeavBJQ - closed, transferred 2026-08-28 to a/c ...008 - ties exactly: opening 0 + events 505,434 = 505,434</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Settlement 28/08/2026 - 04/09/2026  #-tQ1ArXEHgVJvSrggnUO2r5BK42DF-NRLJIHrGUtZ18</t>
+          <t>Settlement 28/08/2026 - 04/09/2026  #-tQ1ArXE</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>closed, transferred 2026-09-04 to a/c ...008 - ties exactly: opening 0 + events 1,088,816 = 1,088,816</t>
+          <t>group -tQ1ArXEHgVJvSrggnUO2r5BK42DF-NRLJIHrGUtZ18 - closed, transferred 2026-09-04 to a/c ...008 - ties exactly: opening 0 + events 1,088,816 = 1,088,816</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Settlement 28/08/2026 - 04/09/2026  #vcTJvhcLLIZ7-2r7tcpy_gYTWS0BO6-A4zB8xOcrcyU</t>
+          <t>Settlement 28/08/2026 - 04/09/2026  #vcTJvhcL</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>closed, transferred 2026-09-04 to a/c ...008 - ties exactly: opening 0 + events 430,361 = 430,361</t>
+          <t>group vcTJvhcLLIZ7-2r7tcpy_gYTWS0BO6-A4zB8xOcrcyU - closed, transferred 2026-09-04 to a/c ...008 - ties exactly: opening 0 + events 430,361 = 430,361</t>
         </is>
       </c>
     </row>

--- a/data/processed/reconciliation_NEXLEV_2026-08.xlsx
+++ b/data/processed/reconciliation_NEXLEV_2026-08.xlsx
@@ -1280,7 +1280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D117"/>
+  <dimension ref="A1:D119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1480,49 +1480,53 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shipping and gift wrap collected</t>
+          <t xml:space="preserve">  of which Nexlev</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>66766.37</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
+        <v>11605025.03</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>99.9% of the account, 3699 units</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>02. RETURNS</t>
+          <t>01. SALES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Units refunded</t>
+          <t xml:space="preserve">  of which Fossil</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>567</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
+        <v>16262.71</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.1% of the account, 16 units - landed cost and ad spend below are for nexlev, so THIS brand's costs are NOT in them</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02. RETURNS</t>
+          <t>01. SALES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Return rate % (in-month, mixed cohorts)</t>
+          <t>Shipping and gift wrap collected</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15.26</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>on Amazon-only units; these refunds mostly belong to earlier months</t>
-        </is>
-      </c>
+        <v>66766.37</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1532,11 +1536,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sale value refunded (GST NOT included)</t>
+          <t>Units refunded</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-1753159.5</v>
+        <v>567</v>
       </c>
       <c r="D14" t="inlineStr"/>
     </row>
@@ -1548,15 +1552,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Shipping and gift wrap refunded</t>
+          <t>Return rate % (in-month, mixed cohorts)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-13028.75</v>
+        <v>15.26</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>returned to the customer along with the sale value</t>
+          <t>on Amazon-only units; these refunds mostly belong to earlier months</t>
         </is>
       </c>
     </row>
@@ -1568,17 +1572,13 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Commission on refunds (ex-GST)</t>
+          <t>Sale value refunded (GST NOT included)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>125100.29</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>given back to us</t>
-        </is>
-      </c>
+        <v>-1753159.5</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1588,15 +1588,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FixedClosingFee on refunds (ex-GST)</t>
+          <t>Shipping and gift wrap refunded</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12623</v>
+        <v>-13028.75</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>given back to us</t>
+          <t>returned to the customer along with the sale value</t>
         </is>
       </c>
     </row>
@@ -1608,11 +1608,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GiftwrapChargeback on refunds (ex-GST)</t>
+          <t>Commission on refunds (ex-GST)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>25.42</v>
+        <v>125100.29</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1628,15 +1628,15 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RefundCommission on refunds (ex-GST)</t>
+          <t>FixedClosingFee on refunds (ex-GST)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-31750</v>
+        <v>12623</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Amazon kept this</t>
+          <t>given back to us</t>
         </is>
       </c>
     </row>
@@ -1648,11 +1648,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ShippingChargeback on refunds (ex-GST)</t>
+          <t>GiftwrapChargeback on refunds (ex-GST)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>870.34</v>
+        <v>25.42</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1663,34 +1663,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>03. AMAZON FEES (ex-GST)</t>
+          <t>02. RETURNS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Commission (referral)</t>
+          <t>RefundCommission on refunds (ex-GST)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-826239.8100000001</v>
-      </c>
-      <c r="D21" t="inlineStr"/>
+        <v>-31750</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Amazon kept this</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>03. AMAZON FEES (ex-GST)</t>
+          <t>02. RETURNS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FBA fulfilment</t>
+          <t>ShippingChargeback on refunds (ex-GST)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-537860.52</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
+        <v>870.34</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>given back to us</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1700,11 +1708,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Closing fee</t>
+          <t>Commission (referral)</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-177166</v>
+        <v>-826239.8100000001</v>
       </c>
       <c r="D23" t="inlineStr"/>
     </row>
@@ -1716,11 +1724,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Other selling fees</t>
+          <t>FBA fulfilment</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-4586.44</v>
+        <v>-537860.52</v>
       </c>
       <c r="D24" t="inlineStr"/>
     </row>
@@ -1732,17 +1740,13 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FBAStorageFee</t>
+          <t>Closing fee</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-111891.38</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>FBA Inventory Storage Fee</t>
-        </is>
-      </c>
+        <v>-177166</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1752,17 +1756,13 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FBALongTermStorageFee</t>
+          <t>Other selling fees</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-18510.93</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>FBA Long Term Storage Fee</t>
-        </is>
-      </c>
+        <v>-4586.44</v>
+      </c>
+      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1772,15 +1772,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FBARemovalFee</t>
+          <t>FBAStorageFee</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-9320</v>
+        <v>-111891.38</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FBA Removal Order: Return Fee</t>
+          <t>FBA Inventory Storage Fee</t>
         </is>
       </c>
     </row>
@@ -1792,15 +1792,15 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MFNPostageFee</t>
+          <t>FBALongTermStorageFee</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-1199</v>
+        <v>-18510.93</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ServiceFee</t>
+          <t>FBA Long Term Storage Fee</t>
         </is>
       </c>
     </row>
@@ -1812,15 +1812,15 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TechnologyFee</t>
+          <t>FBARemovalFee</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>-9320</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>RefusedDelivery</t>
+          <t>FBA Removal Order: Return Fee</t>
         </is>
       </c>
     </row>
@@ -1832,15 +1832,15 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TechnologyFee</t>
+          <t>MFNPostageFee</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>-1199</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ShippingAddressUndeliverable</t>
+          <t>ServiceFee</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>UnableToDeliver</t>
+          <t>RefusedDelivery</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Subscription</t>
+          <t>TechnologyFee</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ServiceFee</t>
+          <t>ShippingAddressUndeliverable</t>
         </is>
       </c>
     </row>
@@ -1892,11 +1892,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FBAPerUnitFulfillmentFee</t>
+          <t>TechnologyFee</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>204.36</v>
+        <v>0</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1912,15 +1912,15 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FBAWeightBasedFee</t>
+          <t>Subscription</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>UnableToDeliver</t>
+          <t>ServiceFee</t>
         </is>
       </c>
     </row>
@@ -1936,11 +1936,11 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1639.65</v>
+        <v>204.36</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ShippingAddressUndeliverable</t>
+          <t>UnableToDeliver</t>
         </is>
       </c>
     </row>
@@ -1952,15 +1952,15 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FBAPerUnitFulfillmentFee</t>
+          <t>FBAWeightBasedFee</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4343.62</v>
+        <v>1001</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>RefusedDelivery</t>
+          <t>UnableToDeliver</t>
         </is>
       </c>
     </row>
@@ -1972,11 +1972,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FBAWeightBasedFee</t>
+          <t>FBAPerUnitFulfillmentFee</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7577</v>
+        <v>1639.65</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1992,11 +1992,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FBAWeightBasedFee</t>
+          <t>FBAPerUnitFulfillmentFee</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>18695</v>
+        <v>4343.62</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2012,51 +2012,55 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Multi-Channel Fulfilment (other channels)</t>
+          <t>FBAWeightBasedFee</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-58344</v>
+        <v>7577</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>418 units Amazon shipped for orders placed elsewhere - real cash, but it belongs to that channel, not to Amazon 3P</t>
+          <t>ShippingAddressUndeliverable</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>04. WE FUNDED</t>
+          <t>03. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Coupons / promotions</t>
+          <t>FBAWeightBasedFee</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-130274.96</v>
-      </c>
-      <c r="D40" t="inlineStr"/>
+        <v>18695</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>RefusedDelivery</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>04. WE FUNDED</t>
+          <t>03. AMAZON FEES (ex-GST)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  of which PromotionMetaDataDefinitionValue</t>
+          <t>Multi-Channel Fulfilment (other channels)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-130274.96</v>
+        <v>-58344</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Amazon returns no real promotion type here, so this does NOT tell us whether coupons ran - the missing coupon-redemption fee stays an open question</t>
+          <t>418 units Amazon shipped for orders placed elsewhere - real cash, but it belongs to that channel, not to Amazon 3P</t>
         </is>
       </c>
     </row>
@@ -2068,11 +2072,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>No-cost EMI / bank offers</t>
+          <t>Coupons / promotions</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-69514.82000000001</v>
+        <v>-130274.96</v>
       </c>
       <c r="D42" t="inlineStr"/>
     </row>
@@ -2084,15 +2088,15 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Advertising (billed with GST)</t>
+          <t xml:space="preserve">  of which PromotionMetaDataDefinitionValue</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-1364759.55</v>
+        <v>-130274.96</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>what Amazon Ads actually charged us, GST included</t>
+          <t>Amazon returns no real promotion type here, so this does NOT tell us whether coupons ran - the missing coupon-redemption fee stays an open question</t>
         </is>
       </c>
     </row>
@@ -2104,17 +2108,13 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">  of which GST we get back as credit</t>
+          <t>No-cost EMI / bank offers</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>208183.66</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>reclaimed below - the real cost of ads is the ex-GST figure</t>
-        </is>
-      </c>
+        <v>-69514.82000000001</v>
+      </c>
+      <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2124,55 +2124,55 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  real cost of advertising (ex-GST)</t>
+          <t>Advertising (billed with GST)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-1156575.89</v>
+        <v>-1364759.55</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10.0% of sales</t>
+          <t>what Amazon Ads actually charged us, GST included</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>05. CREDITS</t>
+          <t>04. WE FUNDED</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Reversal Reimbursement</t>
+          <t xml:space="preserve">  of which GST we get back as credit</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>101864.35</v>
+        <v>208183.66</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>compensation - no GST</t>
+          <t>reclaimed below - the real cost of ads is the ex-GST figure</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>05. CREDITS</t>
+          <t>04. WE FUNDED</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Free Replacement Refund Items</t>
+          <t xml:space="preserve">  real cost of advertising (ex-GST)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>42851.01</v>
+        <v>-1156575.89</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>compensation - no GST</t>
+          <t>10.0% of sales</t>
         </is>
       </c>
     </row>
@@ -2184,11 +2184,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Lostordamagedreimbursement</t>
+          <t>Reversal Reimbursement</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1114.52</v>
+        <v>101864.35</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2204,11 +2204,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Warehouse Damage</t>
+          <t>Free Replacement Refund Items</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1821.61</v>
+        <v>42851.01</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2224,15 +2224,15 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Commissioncorrection</t>
+          <t>Lostordamagedreimbursement</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>65468.13</v>
+        <v>1114.52</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>fee credit - carries GST, reverses ITC</t>
+          <t>compensation - no GST</t>
         </is>
       </c>
     </row>
@@ -2244,11 +2244,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Payment Retraction Items</t>
+          <t>Warehouse Damage</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-2230.36</v>
+        <v>1821.61</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2259,38 +2259,42 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06. GST AND TAX (not profit)</t>
+          <t>05. CREDITS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Output GST collected from customers</t>
+          <t>Commissioncorrection</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2062051.32</v>
+        <v>65468.13</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>held in trust - never ours</t>
+          <t>fee credit - carries GST, reverses ITC</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06. GST AND TAX (not profit)</t>
+          <t>05. CREDITS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Output GST reversed on refunds</t>
+          <t>Payment Retraction Items</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-310107.66</v>
-      </c>
-      <c r="D53" t="inlineStr"/>
+        <v>-2230.36</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>compensation - no GST</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2300,15 +2304,15 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ITC on Amazon fees (reclaimable)</t>
+          <t>Output GST collected from customers</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>288861.91</v>
+        <v>2062051.32</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>tie to Amazon's tax invoice AND GSTR-2B</t>
+          <t>held in trust - never ours</t>
         </is>
       </c>
     </row>
@@ -2320,17 +2324,13 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ITC on no-cost EMI (reclaimable)</t>
+          <t>Output GST reversed on refunds</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>10604.02</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>the EMI expense Amazon bills carries GST as well</t>
-        </is>
-      </c>
+        <v>-310107.66</v>
+      </c>
+      <c r="D55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2340,15 +2340,15 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ITC on advertising (reclaimable)</t>
+          <t>ITC on Amazon fees (reclaimable)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>208183.66</v>
+        <v>288861.91</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ad invoices carry GST too - claim it in GSTR-2B or you pay 18% twice</t>
+          <t>tie to Amazon's tax invoice AND GSTR-2B</t>
         </is>
       </c>
     </row>
@@ -2360,15 +2360,15 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TCS withheld u/s 52 (0.5% of net sales)</t>
+          <t>ITC on no-cost EMI (reclaimable)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-49015.15</v>
+        <v>10604.02</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>PREPAYMENT ASSET - accept monthly in the GST portal or it is stranded</t>
+          <t>the EMI expense Amazon bills carries GST as well</t>
         </is>
       </c>
     </row>
@@ -2380,15 +2380,15 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TDS withheld u/s 194-O (0.1% of gross)</t>
+          <t>ITC on advertising (reclaimable)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-11592.94</v>
+        <v>208183.66</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>RECOVERABLE in ITR - charged on gross, so returns are a permanent drag</t>
+          <t>ad invoices carry GST too - claim it in GSTR-2B or you pay 18% twice</t>
         </is>
       </c>
     </row>
@@ -2400,55 +2400,55 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Net GST still to remit in cash</t>
+          <t>TCS withheld u/s 52 (0.5% of net sales)</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-1195278.92</v>
+        <v>-49015.15</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>marketplace GST only - import IGST paid at the bill of entry is also creditable and is NOT netted here</t>
+          <t>PREPAYMENT ASSET - accept monthly in the GST portal or it is stranded</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07. HOW THE TOTAL IS BUILT</t>
+          <t>06. GST AND TAX (not profit)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Product sales (GST not included)</t>
+          <t>TDS withheld u/s 194-O (0.1% of gross)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>11621287.74</v>
+        <v>-11592.94</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>what we sold</t>
+          <t>RECOVERABLE in ITR - charged on gross, so returns are a permanent drag</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07. HOW THE TOTAL IS BUILT</t>
+          <t>06. GST AND TAX (not profit)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>plus GST collected from customers</t>
+          <t>Net GST still to remit in cash</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2062051.32</v>
+        <v>-1195278.92</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>comes in with the sale, goes out to the government</t>
+          <t>marketplace GST only - import IGST paid at the bill of entry is also creditable and is NOT netted here</t>
         </is>
       </c>
     </row>
@@ -2460,13 +2460,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>plus shipping and gift wrap</t>
+          <t>Product sales (GST not included)</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>66766.37</v>
-      </c>
-      <c r="D62" t="inlineStr"/>
+        <v>11621287.74</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>what we sold</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2476,15 +2480,15 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>less refunds to customers</t>
+          <t>plus GST collected from customers</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-2076295.91</v>
+        <v>2062051.32</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>sale value + GST returned</t>
+          <t>comes in with the sale, goes out to the government</t>
         </is>
       </c>
     </row>
@@ -2496,17 +2500,13 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>plus fees Amazon returned on refunds</t>
+          <t>plus shipping and gift wrap</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>126105.48</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>commission and closing come back; FBA fee does not</t>
-        </is>
-      </c>
+        <v>66766.37</v>
+      </c>
+      <c r="D64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2516,15 +2516,15 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>less Amazon fees (including GST on fees)</t>
+          <t>less refunds to customers</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-2019755.79</v>
+        <v>-2076295.91</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>commission, FBA, closing, storage, removals</t>
+          <t>sale value + GST returned</t>
         </is>
       </c>
     </row>
@@ -2536,13 +2536,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>less coupons and promotions</t>
+          <t>plus fees Amazon returned on refunds</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-130274.96</v>
-      </c>
-      <c r="D66" t="inlineStr"/>
+        <v>126105.48</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>commission and closing come back; FBA fee does not</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2552,13 +2556,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>less no-cost EMI and bank offers</t>
+          <t>less Amazon fees (including GST on fees)</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-69514.82000000001</v>
-      </c>
-      <c r="D67" t="inlineStr"/>
+        <v>-2019755.79</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>commission, FBA, closing, storage, removals</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2568,11 +2576,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>plus reimbursements and corrections</t>
+          <t>less coupons and promotions</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>210889.26</v>
+        <v>-130274.96</v>
       </c>
       <c r="D68" t="inlineStr"/>
     </row>
@@ -2584,17 +2592,13 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>less TCS withheld</t>
+          <t>less no-cost EMI and bank offers</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-49015.15</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>you reclaim this in GST</t>
-        </is>
-      </c>
+        <v>-69514.82000000001</v>
+      </c>
+      <c r="D69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2604,55 +2608,51 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>less TDS withheld</t>
+          <t>plus reimbursements and corrections</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-11592.94</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>you reclaim this in your ITR</t>
-        </is>
-      </c>
+        <v>210889.26</v>
+      </c>
+      <c r="D70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08. BOTTOM LINE</t>
+          <t>07. HOW THE TOTAL IS BUILT</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AMAZON SHOULD PAY US</t>
+          <t>less TCS withheld</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>9730650.6</v>
+        <v>-49015.15</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>add up everything above - this is the settlement</t>
+          <t>you reclaim this in GST</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08. BOTTOM LINE</t>
+          <t>07. HOW THE TOTAL IS BUILT</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>less GST we owe the government</t>
+          <t>less TDS withheld</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-1195278.92</v>
+        <v>-11592.94</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>output GST, less refunds, less credit on fee GST and ad GST, less TCS withheld</t>
+          <t>you reclaim this in your ITR</t>
         </is>
       </c>
     </row>
@@ -2664,15 +2664,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MARKETPLACE CONTRIBUTION BEFORE COGS</t>
+          <t>AMAZON SHOULD PAY US</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>8535371.68</v>
+        <v>9730650.6</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>what the marketplace actually left us</t>
+          <t>add up everything above - this is the settlement</t>
         </is>
       </c>
     </row>
@@ -2684,15 +2684,15 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>less advertising (GST-inclusive cash)</t>
+          <t>less GST we owe the government</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-1364759.55</v>
+        <v>-1195278.92</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>billed separately by Amazon Ads; its GST is credited back in the line above</t>
+          <t>output GST, less refunds, less credit on fee GST and ad GST, less TCS withheld</t>
         </is>
       </c>
     </row>
@@ -2704,15 +2704,15 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AFTER ADVERTISING, BEFORE COGS</t>
+          <t>MARKETPLACE CONTRIBUTION BEFORE COGS</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>7170612.13</v>
+        <v>8535371.68</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>the landed cost of the goods still has to come off</t>
+          <t>what the marketplace actually left us</t>
         </is>
       </c>
     </row>
@@ -2724,15 +2724,15 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>add back TDS withheld (recoverable in your ITR)</t>
+          <t>less advertising (GST-inclusive cash)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>11592.94</v>
+        <v>-1364759.55</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>reduces the cash Amazon sends, but it is not a cost</t>
+          <t>billed separately by Amazon Ads; its GST is credited back in the line above</t>
         </is>
       </c>
     </row>
@@ -2744,55 +2744,55 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>add back Multi-Channel Fulfilment fee</t>
+          <t>AFTER ADVERTISING, BEFORE COGS</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>58344</v>
+        <v>7170612.13</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>418 units Amazon shipped for orders placed on another channel - real cash, but that channel's cost, not Amazon's (ex-GST; the GST on it is already credited in the line above)</t>
+          <t>the landed cost of the goods still has to come off</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09. COST OF GOODS</t>
+          <t>08. BOTTOM LINE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Landed cost of units shipped</t>
+          <t>add back TDS withheld (recoverable in your ITR)</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-5914157.89</v>
+        <v>11592.94</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>3715 units at Rs 1,592 average (96% priced from the Nexlev master, rest at that average)</t>
+          <t>reduces the cash Amazon sends, but it is not a cost</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09. COST OF GOODS</t>
+          <t>08. BOTTOM LINE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">  of which priced on an ASSUMPTION</t>
+          <t>add back Multi-Channel Fulfilment fee</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-210139.66</v>
+        <v>58344</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>132 units across 20 SKUs have no row in the Nexlev master - see the 'Unmapped SKUs' sheet; map them and this line becomes measured</t>
+          <t>418 units Amazon shipped for orders placed on another channel - real cash, but that channel's cost, not Amazon's (ex-GST; the GST on it is already credited in the line above)</t>
         </is>
       </c>
     </row>
@@ -2804,15 +2804,15 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>less stock recovered from returns</t>
+          <t>Landed cost of units shipped</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>480962.94</v>
+        <v>-5914157.89</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>567 refunds, 61% came back sellable, valued at 88% (repack + restarted storage clock)</t>
+          <t>3715 units at Rs 1,592 average (96% priced from the Nexlev master, rest at that average)</t>
         </is>
       </c>
     </row>
@@ -2824,15 +2824,15 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Inbound freight to FBA - NOT INCLUDED</t>
+          <t xml:space="preserve">  of which priced on an ASSUMPTION</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>-210139.66</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>we self-ship into FBA, so this never appears in Amazon's data and it is not in the margin master either - profit below is overstated by it. Re-run with --freight-per-unit &lt;Rs&gt; to book it</t>
+          <t>132 units across 20 SKUs have no row in the Nexlev master - see the 'Unmapped SKUs' sheet; map them and this line becomes measured</t>
         </is>
       </c>
     </row>
@@ -2844,53 +2844,53 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NET COST OF GOODS</t>
+          <t>less stock recovered from returns</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-5433194.95</v>
-      </c>
-      <c r="D82" t="inlineStr"/>
+        <v>480962.94</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>567 refunds, 61% came back sellable, valued at 88% (repack + restarted storage clock)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10. PROFIT</t>
+          <t>09. COST OF GOODS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AMAZON CHANNEL CONTRIBUTION</t>
+          <t>Inbound freight to FBA - NOT INCLUDED</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1807354.13</v>
+        <v>0</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>15.6% of sales - before company overhead, interest and tax</t>
+          <t>we self-ship into FBA, so this never appears in Amazon's data and it is not in the margin master either - profit below is overstated by it. Re-run with --freight-per-unit &lt;Rs&gt; to book it</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10. PROFIT</t>
+          <t>09. COST OF GOODS</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>less business overhead</t>
+          <t>NET COST OF GOODS</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-295707.89</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>5% of landed cost - same basis as the margin calculator</t>
-        </is>
-      </c>
+        <v>-5433194.95</v>
+      </c>
+      <c r="D84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2900,15 +2900,15 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>less cost of finance</t>
+          <t>AMAZON CHANNEL CONTRIBUTION</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-177424.74</v>
+        <v>1807354.13</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>3% of landed cost - working capital tied up in stock</t>
+          <t>15.6% of sales - before company overhead, interest and tax</t>
         </is>
       </c>
     </row>
@@ -2920,15 +2920,15 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PROFIT BEFORE TAX</t>
+          <t>less business overhead</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1334221.49</v>
+        <v>-295707.89</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>11.5% of sales</t>
+          <t>5% of landed cost - same basis as the margin calculator</t>
         </is>
       </c>
     </row>
@@ -2940,15 +2940,15 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>less income tax provision</t>
+          <t>less cost of finance</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-335796.87</v>
+        <v>-177424.74</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>25.17% under section 115BAA</t>
+          <t>3% of landed cost - working capital tied up in stock</t>
         </is>
       </c>
     </row>
@@ -2960,55 +2960,55 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PROFIT AFTER TAX</t>
+          <t>PROFIT BEFORE TAX</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>998424.63</v>
+        <v>1334221.49</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>8.6% of sales</t>
+          <t>11.5% of sales</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>12. COMPLETENESS</t>
+          <t>10. PROFIT</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Event lists Amazon returned with data</t>
+          <t>less income tax provision</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>6</v>
+        <v>-335796.87</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>AdjustmentEventList, AffordabilityExpenseEventList, AffordabilityExpenseReversalEventList, RefundEventList, ServiceFeeEventList, ShipmentEventList</t>
+          <t>25.17% under section 115BAA</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>12. COMPLETENESS</t>
+          <t>10. PROFIT</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Event lists returned EMPTY</t>
+          <t>PROFIT AFTER TAX</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>29</v>
+        <v>998424.63</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>incl. ShipmentSettleEventList - must stay empty or revenue double-counts</t>
+          <t>8.6% of sales</t>
         </is>
       </c>
     </row>
@@ -3020,15 +3020,15 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Money in ShipmentEventList we did not classify</t>
+          <t>Event lists Amazon returned with data</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-0</v>
+        <v>6</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>MUST BE ZERO - this is measured, not asserted</t>
+          <t>AdjustmentEventList, AffordabilityExpenseEventList, AffordabilityExpenseReversalEventList, RefundEventList, ServiceFeeEventList, ShipmentEventList</t>
         </is>
       </c>
     </row>
@@ -3040,15 +3040,15 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Money in RefundEventList we did not classify</t>
+          <t>Event lists returned EMPTY</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-0</v>
+        <v>29</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>MUST BE ZERO - this is measured, not asserted</t>
+          <t>incl. ShipmentSettleEventList - must stay empty or revenue double-counts</t>
         </is>
       </c>
     </row>
@@ -3060,11 +3060,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Money in ServiceFeeEventList we did not classify</t>
+          <t>Money in ShipmentEventList we did not classify</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -3080,15 +3080,15 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Money in AdjustmentEventList we did not classify</t>
+          <t>Money in RefundEventList we did not classify</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>zero by construction - we book Amazon's parent total; the real test for this list is the breakdown check below</t>
+          <t>MUST BE ZERO - this is measured, not asserted</t>
         </is>
       </c>
     </row>
@@ -3100,15 +3100,15 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Money in AffordabilityExpenseEventList we did not classify</t>
+          <t>Money in ServiceFeeEventList we did not classify</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>zero by construction - we book Amazon's parent total; the real test for this list is the breakdown check below</t>
+          <t>MUST BE ZERO - this is measured, not asserted</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Money in AffordabilityExpenseReversalEventList we did not classify</t>
+          <t>Money in AdjustmentEventList we did not classify</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -3140,55 +3140,55 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Breakdowns that disagree with their parent</t>
+          <t>Money in AffordabilityExpenseEventList we did not classify</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>every AdjustmentItemList and Affordability base+GST re-added to the parent total we booked</t>
+          <t>zero by construction - we book Amazon's parent total; the real test for this list is the breakdown check below</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>13. BANK TIE-OUT</t>
+          <t>12. COMPLETENESS</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Settlement 31/07/2026 - 07/08/2026  #EpyKFnvK</t>
+          <t>Money in AffordabilityExpenseReversalEventList we did not classify</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1725070.29</v>
+        <v>0</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>group EpyKFnvKPO0UseyGWOBhBsbWbtBrllFygs_m0sIQ7Rw - closed, transferred 2026-08-07 to a/c ...008 - ties exactly: opening 0 + events 1,725,070 = 1,725,070</t>
+          <t>zero by construction - we book Amazon's parent total; the real test for this list is the breakdown check below</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>13. BANK TIE-OUT</t>
+          <t>12. COMPLETENESS</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Settlement 31/07/2026 - 07/08/2026  #BYibnRov</t>
+          <t>Breakdowns that disagree with their parent</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>480833.4</v>
+        <v>0</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>group BYibnRovNZHg1P4a8L9B8K7gAVqzLkp9aSWIGiYT8a8 - closed, transferred 2026-08-07 to a/c ...008 - ties exactly: opening 0 + events 480,833 = 480,833</t>
+          <t>every AdjustmentItemList and Affordability base+GST re-added to the parent total we booked</t>
         </is>
       </c>
     </row>
@@ -3200,15 +3200,15 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Settlement 07/08/2026 - 14/08/2026  #qi1SEXQF</t>
+          <t>Settlement 31/07/2026 - 07/08/2026  #EpyKFnvK</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1689832.41</v>
+        <v>1725070.29</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>group qi1SEXQFEWltMlJJ3u3-78uykuEVcNxBSFviVstqx40 - closed, transferred 2026-08-14 to a/c ...008 - ties exactly: opening 0 + events 1,689,832 = 1,689,832</t>
+          <t>group EpyKFnvKPO0UseyGWOBhBsbWbtBrllFygs_m0sIQ7Rw - closed, transferred 2026-08-07 to a/c ...008 - ties exactly: opening 0 + events 1,725,070 = 1,725,070</t>
         </is>
       </c>
     </row>
@@ -3220,15 +3220,15 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Settlement 07/08/2026 - 14/08/2026  #nbrNd14g</t>
+          <t>Settlement 31/07/2026 - 07/08/2026  #BYibnRov</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>559243.8199999999</v>
+        <v>480833.4</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>group nbrNd14gFT6XF6hDagxzKzPV8ElXYzRIHo5IIVFV-SQ - closed, transferred 2026-08-14 to a/c ...008 - ties exactly: opening 0 + events 559,244 = 559,244</t>
+          <t>group BYibnRovNZHg1P4a8L9B8K7gAVqzLkp9aSWIGiYT8a8 - closed, transferred 2026-08-07 to a/c ...008 - ties exactly: opening 0 + events 480,833 = 480,833</t>
         </is>
       </c>
     </row>
@@ -3240,15 +3240,15 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Settlement 14/08/2026 - 21/08/2026  #S9Fkp3FT</t>
+          <t>Settlement 07/08/2026 - 14/08/2026  #qi1SEXQF</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2093650.61</v>
+        <v>1689832.41</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>group S9Fkp3FTRgkf6dWA_Qs-qndkx0jUBjHtywDnlAxTWOM - closed, transferred 2026-08-21 to a/c ...008 - ties exactly: opening 0 + events 2,093,651 = 2,093,651</t>
+          <t>group qi1SEXQFEWltMlJJ3u3-78uykuEVcNxBSFviVstqx40 - closed, transferred 2026-08-14 to a/c ...008 - ties exactly: opening 0 + events 1,689,832 = 1,689,832</t>
         </is>
       </c>
     </row>
@@ -3260,15 +3260,15 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Settlement 14/08/2026 - 21/08/2026  #pJVgmCSY</t>
+          <t>Settlement 07/08/2026 - 14/08/2026  #nbrNd14g</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>614959.29</v>
+        <v>559243.8199999999</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>group pJVgmCSYEdE5Mhopb6W58kOcPUwryJ1XpO8-lk2bLnw - closed, transferred 2026-08-21 to a/c ...008 - ties exactly: opening 0 + events 614,959 = 614,959</t>
+          <t>group nbrNd14gFT6XF6hDagxzKzPV8ElXYzRIHo5IIVFV-SQ - closed, transferred 2026-08-14 to a/c ...008 - ties exactly: opening 0 + events 559,244 = 559,244</t>
         </is>
       </c>
     </row>
@@ -3280,15 +3280,15 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Settlement 21/08/2026 - 28/08/2026  #C61MFNpQ</t>
+          <t>Settlement 14/08/2026 - 21/08/2026  #S9Fkp3FT</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1467714.36</v>
+        <v>2093650.61</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>group C61MFNpQJBP4bDB2LdFzKaqpFcCVxqsdOtDKxsfmc5w - closed, transferred 2026-08-28 to a/c ...008 - ties exactly: opening 0 + events 1,467,714 = 1,467,714</t>
+          <t>group S9Fkp3FTRgkf6dWA_Qs-qndkx0jUBjHtywDnlAxTWOM - closed, transferred 2026-08-21 to a/c ...008 - ties exactly: opening 0 + events 2,093,651 = 2,093,651</t>
         </is>
       </c>
     </row>
@@ -3300,15 +3300,15 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Settlement 21/08/2026 - 28/08/2026  #QNwQb0I2</t>
+          <t>Settlement 14/08/2026 - 21/08/2026  #pJVgmCSY</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>505434</v>
+        <v>614959.29</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>group QNwQb0I2fYRMNherxVceFyNVbUB0pHXEzfw4YeavBJQ - closed, transferred 2026-08-28 to a/c ...008 - ties exactly: opening 0 + events 505,434 = 505,434</t>
+          <t>group pJVgmCSYEdE5Mhopb6W58kOcPUwryJ1XpO8-lk2bLnw - closed, transferred 2026-08-21 to a/c ...008 - ties exactly: opening 0 + events 614,959 = 614,959</t>
         </is>
       </c>
     </row>
@@ -3320,15 +3320,15 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Settlement 28/08/2026 - 04/09/2026  #-tQ1ArXE</t>
+          <t>Settlement 21/08/2026 - 28/08/2026  #C61MFNpQ</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1088816.38</v>
+        <v>1467714.36</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>group -tQ1ArXEHgVJvSrggnUO2r5BK42DF-NRLJIHrGUtZ18 - closed, transferred 2026-09-04 to a/c ...008 - ties exactly: opening 0 + events 1,088,816 = 1,088,816</t>
+          <t>group C61MFNpQJBP4bDB2LdFzKaqpFcCVxqsdOtDKxsfmc5w - closed, transferred 2026-08-28 to a/c ...008 - ties exactly: opening 0 + events 1,467,714 = 1,467,714</t>
         </is>
       </c>
     </row>
@@ -3340,15 +3340,15 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Settlement 28/08/2026 - 04/09/2026  #vcTJvhcL</t>
+          <t>Settlement 21/08/2026 - 28/08/2026  #QNwQb0I2</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>430360.71</v>
+        <v>505434</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>group vcTJvhcLLIZ7-2r7tcpy_gYTWS0BO6-A4zB8xOcrcyU - closed, transferred 2026-09-04 to a/c ...008 - ties exactly: opening 0 + events 430,361 = 430,361</t>
+          <t>group QNwQb0I2fYRMNherxVceFyNVbUB0pHXEzfw4YeavBJQ - closed, transferred 2026-08-28 to a/c ...008 - ties exactly: opening 0 + events 505,434 = 505,434</t>
         </is>
       </c>
     </row>
@@ -3360,15 +3360,15 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CASH Amazon actually transferred this month</t>
+          <t>Settlement 28/08/2026 - 04/09/2026  #-tQ1ArXE</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>9136738.18</v>
+        <v>1088816.38</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>sum of settlements whose transfer date falls inside the month - this is what should appear on the bank statement</t>
+          <t>group -tQ1ArXEHgVJvSrggnUO2r5BK42DF-NRLJIHrGUtZ18 - closed, transferred 2026-09-04 to a/c ...008 - ties exactly: opening 0 + events 1,088,816 = 1,088,816</t>
         </is>
       </c>
     </row>
@@ -3380,15 +3380,15 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Accrual: what this month's events say we earned</t>
+          <t>Settlement 28/08/2026 - 04/09/2026  #vcTJvhcL</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>9730650.6</v>
+        <v>430360.71</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>section 08 - events POSTED in the month, whenever they get paid</t>
+          <t>group vcTJvhcLLIZ7-2r7tcpy_gYTWS0BO6-A4zB8xOcrcyU - closed, transferred 2026-09-04 to a/c ...008 - ties exactly: opening 0 + events 430,361 = 430,361</t>
         </is>
       </c>
     </row>
@@ -3400,15 +3400,15 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Timing difference (accrual less cash)</t>
+          <t>CASH Amazon actually transferred this month</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>593912.42</v>
+        <v>9136738.18</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>settlement periods straddle month ends - a difference here is TIMING, not error; it is only a problem if a group above fails to tie</t>
+          <t>sum of settlements whose transfer date falls inside the month - this is what should appear on the bank statement</t>
         </is>
       </c>
     </row>
@@ -3420,55 +3420,55 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Groups re-derived from their own events</t>
+          <t>Accrual: what this month's events say we earned</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>10</v>
+        <v>9730650.6</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>10 of 10 tie to the rupee</t>
+          <t>section 08 - events POSTED in the month, whenever they get paid</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>14. RETURNS - COHORT VIEW (memo)</t>
+          <t>13. BANK TIE-OUT</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Return rate used above (in-month)</t>
+          <t>Timing difference (accrual less cash)</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>15.26</v>
+        <v>593912.42</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>refunds POSTED this month over units shipped this month - two different populations, which is why this is only a proxy</t>
+          <t>settlement periods straddle month ends - a difference here is TIMING, not error; it is only a problem if a group above fails to tie</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>14. RETURNS - COHORT VIEW (memo)</t>
+          <t>13. BANK TIE-OUT</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Returns already arrived from this month's orders</t>
+          <t>Groups re-derived from their own events</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>10.72</v>
+        <v>10</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>after 0 month(s); matured cohorts say that is only 67% of what a cohort ever returns</t>
+          <t>10 of 10 tie to the rupee</t>
         </is>
       </c>
     </row>
@@ -3480,15 +3480,15 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EXPECTED LIFETIME return rate for this month's orders</t>
+          <t>Return rate used above (in-month)</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>15.89</v>
+        <v>15.26</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>grossed up on the curve from cohorts at least 3 months old (their lifetime rate: 15.60%)</t>
+          <t>refunds POSTED this month over units shipped this month - two different populations, which is why this is only a proxy</t>
         </is>
       </c>
     </row>
@@ -3500,15 +3500,15 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Units this month's shipments will return</t>
+          <t>Returns already arrived from this month's orders</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>590</v>
+        <v>10.72</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>the cohort rate applied to the 3,715 units this P&amp;L is built on (the cohort itself is 4,131 units ordered in the month); vs 567 refunds actually posted</t>
+          <t>after 0 month(s); matured cohorts say that is only 67% of what a cohort ever returns</t>
         </is>
       </c>
     </row>
@@ -3520,15 +3520,15 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Net cost of one return</t>
+          <t>EXPECTED LIFETIME return rate for this month's orders</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>-2021.32</v>
+        <v>16.05</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Rs3,092 sale value given back, less Rs222 of fees returned, less Rs848 of stock that comes back sellable</t>
+          <t>grossed up on the curve from cohorts at least 2 months old (their lifetime rate: 15.74%)</t>
         </is>
       </c>
     </row>
@@ -3540,15 +3540,55 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
+          <t>Units this month's shipments will return</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>596</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>the cohort rate applied to the 3,715 units this P&amp;L is built on (the cohort itself is 4,131 units ordered in the month); vs 567 refunds actually posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>14. RETURNS - COHORT VIEW (memo)</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Net cost of one return</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>-2021.32</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Rs3,092 sale value given back, less Rs222 of fees returned, less Rs848 of stock that comes back sellable</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>14. RETURNS - COHORT VIEW (memo)</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
           <t>PROVISION if charged on a cohort basis</t>
         </is>
       </c>
-      <c r="C117" t="n">
-        <v>-47236.79</v>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>+23 more returns than the month booked. The bottom line above is NOT adjusted for this - it stays on the settlement basis that section 13 ties to the bank</t>
+      <c r="C119" t="n">
+        <v>-58928.65</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>+29 more returns than the month booked. The bottom line above is NOT adjusted for this - it stays on the settlement basis that section 13 ties to the bank</t>
         </is>
       </c>
     </row>
